--- a/output/tables/2025/tabla6_v_test.xlsx
+++ b/output/tables/2025/tabla6_v_test.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t xml:space="preserve">aviso</t>
   </si>
@@ -36,6 +36,9 @@
     <t xml:space="preserve">categoria</t>
   </si>
   <si>
+    <t xml:space="preserve">lift_pp</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cla/Mod</t>
   </si>
   <si>
@@ -54,6 +57,12 @@
     <t xml:space="preserve">1</t>
   </si>
   <si>
+    <t xml:space="preserve">comper_pct_rec_tercil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bajas prácticas de evitación</t>
+  </si>
+  <si>
     <t xml:space="preserve">emper_ep_pct_rec_tercil</t>
   </si>
   <si>
@@ -72,12 +81,6 @@
     <t xml:space="preserve">No cree que será victima de delito</t>
   </si>
   <si>
-    <t xml:space="preserve">comper_pct_rec_tercil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bajas prácticas de evitación</t>
-  </si>
-  <si>
     <t xml:space="preserve">comper_gasto</t>
   </si>
   <si>
@@ -117,37 +120,37 @@
     <t xml:space="preserve">Media inseguridad en el barrio</t>
   </si>
   <si>
+    <t xml:space="preserve">Alta adopción de medidas comunitarias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cree que será victima de delito no violento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alta inseguridad en la casa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cree que será victima de delito violento</t>
+  </si>
+  <si>
     <t xml:space="preserve">Media inseguridad en espacio publico</t>
   </si>
   <si>
+    <t xml:space="preserve">Medias prácticas de evitación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gasta en medidas de seguridad</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alta inseguridad en espacio publico</t>
   </si>
   <si>
+    <t xml:space="preserve">Alta disposición de medidas vivienda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Altas prácticas de evitación</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alta inseguridad en el barrio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alta inseguridad en la casa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cree que será victima de delito no violento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cree que será victima de delito violento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medias prácticas de evitación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Altas prácticas de evitación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gasta en medidas de seguridad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alta disposición de medidas vivienda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alta adopción de medidas comunitarias</t>
   </si>
   <si>
     <t xml:space="preserve">2</t>
@@ -543,11 +546,12 @@
     <col min="1" max="1" width="7.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="27.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="45.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="11.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="11.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="11.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="7.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="7.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="7.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="6.71" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="11.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="11.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -575,3077 +579,3434 @@
       <c r="H1" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>61.1701796928434</v>
+        <v>46.55</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>77.4767679949598</v>
+        <v>62.18</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>32.4889400642385</v>
+        <v>79.24</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="2" t="e">
+        <v>32.69</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>55.2448413920542</v>
+        <v>44.99</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>70.6331705780438</v>
+        <v>61.17</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>32.7959921620912</v>
+        <v>77.48</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2" t="e">
+        <v>32.49</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>43.0212405787755</v>
+        <v>37.84</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>84.0604819656639</v>
+        <v>55.24</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>50.1201947356726</v>
+        <v>70.63</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2" t="e">
+        <v>32.8</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>62.1802002224694</v>
+        <v>33.94</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>79.2408253268231</v>
+        <v>43.02</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>32.688927943761</v>
+        <v>84.06</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="2" t="e">
+        <v>50.12</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>35.4045085250029</v>
+        <v>20.14</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>73.0981256890849</v>
+        <v>35.4</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>52.9604266408096</v>
+        <v>73.1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="2" t="e">
+        <v>52.96</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>36.986550345329</v>
+        <v>14.74</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>48.0784375492203</v>
+        <v>36.99</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>33.343433731289</v>
+        <v>48.08</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="2" t="e">
+        <v>33.34</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>36.5736226231107</v>
+        <v>14.11</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>47.2594109308553</v>
+        <v>36.57</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>33.1454659313577</v>
+        <v>47.26</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="2" t="e">
+        <v>33.15</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>35.5051821322504</v>
+        <v>12.8</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>46.1332493306032</v>
+        <v>35.51</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>33.3292931741511</v>
+        <v>46.13</v>
       </c>
       <c r="G9" s="2" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="H9" s="2" t="n">
         <v>7.6261156470751e-268</v>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="I9" s="2" t="n">
         <v>34.9651331267459</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>34.347267274619</v>
+        <v>11.19</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>44.195936367932</v>
+        <v>34.35</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>33.0060804395693</v>
+        <v>44.2</v>
       </c>
       <c r="G10" s="2" t="n">
+        <v>33.01</v>
+      </c>
+      <c r="H10" s="2" t="n">
         <v>1.88578809537332e-206</v>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="I10" s="2" t="n">
         <v>30.6609960606726</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>28.7312298619977</v>
+        <v>3.99</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>37.218459599937</v>
+        <v>28.73</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>33.2282891945943</v>
+        <v>37.22</v>
       </c>
       <c r="G11" s="2" t="n">
+        <v>33.23</v>
+      </c>
+      <c r="H11" s="2" t="n">
         <v>0.000000000000000000000000000362635385359878</v>
       </c>
-      <c r="H11" s="2" t="n">
+      <c r="I11" s="2" t="n">
         <v>11.0047213221523</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>26.2487103234812</v>
+        <v>0.78</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>34.0604819656639</v>
+        <v>26.25</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>33.2848514231461</v>
+        <v>34.06</v>
       </c>
       <c r="G12" s="2" t="n">
+        <v>33.28</v>
+      </c>
+      <c r="H12" s="2" t="n">
         <v>0.0316493765074051</v>
       </c>
-      <c r="H12" s="2" t="n">
+      <c r="I12" s="2" t="n">
         <v>2.14881110802096</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.145445730561784</v>
+        <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H13" s="2" t="n">
         <v>0.00000000052975689348314</v>
       </c>
-      <c r="H13" s="2" t="n">
+      <c r="I13" s="2" t="n">
         <v>-6.21002643377842</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>17.6452802805829</v>
+        <v>-10.43</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>22.9799968498976</v>
+        <v>17.65</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>33.4060561986142</v>
+        <v>22.98</v>
       </c>
       <c r="G14" s="2" t="n">
+        <v>33.41</v>
+      </c>
+      <c r="H14" s="2" t="n">
         <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000115108479305011</v>
       </c>
-      <c r="H14" s="2" t="n">
+      <c r="I14" s="2" t="n">
         <v>-29.5310234109178</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="A15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D15" t="n">
-        <v>11.1210869695337</v>
-      </c>
-      <c r="E15" t="n">
-        <v>14.6322255473303</v>
-      </c>
-      <c r="F15" t="n">
-        <v>33.7494697291073</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="e">
+      <c r="B15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>-14.89</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>18.68</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>33.57</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>5.99533297433136</v>
+        <v>-16.23</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>7.89100645770988</v>
+        <v>6.59</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>33.7615902066541</v>
+        <v>5.61</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="2" t="e">
+        <v>21.83</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>4.84728946267408</v>
+        <v>-16.79</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>6.38683257205859</v>
+        <v>12.77</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>33.7979516392946</v>
+        <v>16.65</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="2" t="e">
+        <v>33.44</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>12.76955602537</v>
+        <v>-17.57</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>16.6482910694598</v>
+        <v>9.5</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>33.4424176312547</v>
+        <v>10.33</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="2" t="e">
+        <v>27.9</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" t="s">
-        <v>38</v>
-      </c>
-      <c r="D19" t="n">
-        <v>6.58771280532939</v>
-      </c>
-      <c r="E19" t="n">
-        <v>5.60718223342259</v>
-      </c>
-      <c r="F19" t="n">
-        <v>21.8330202209967</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="e">
+      <c r="A19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>-19.12</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>11.12</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>9.49898638864755</v>
+        <v>-19.15</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>10.3323358009135</v>
+        <v>10.95</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>27.9013393127689</v>
+        <v>14.26</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="2" t="e">
+        <v>33.42</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="s">
-        <v>12</v>
-      </c>
-      <c r="B21" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21" t="s">
-        <v>40</v>
-      </c>
-      <c r="D21" t="n">
-        <v>10.9478902188369</v>
-      </c>
-      <c r="E21" t="n">
-        <v>14.2620885178768</v>
-      </c>
-      <c r="F21" t="n">
-        <v>33.4161565965699</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="e">
+      <c r="A21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>-20.14</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>14.67</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>47.04</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>4.91686036116574</v>
+        <v>-25.87</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>6.49708615530005</v>
+        <v>6</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>33.8949154596691</v>
+        <v>7.89</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="2" t="e">
+        <v>33.76</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>14.6697586532681</v>
+        <v>-25.92</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>26.9018743109151</v>
+        <v>5.89</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>47.0395733591903</v>
+        <v>7.73</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="2" t="e">
+        <v>33.65</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>5.88906231240245</v>
+        <v>-27.4</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>7.72562608284769</v>
+        <v>4.92</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>33.6504858291417</v>
+        <v>6.5</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="2" t="e">
+        <v>33.89</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>14.2736791430978</v>
+        <v>-27.41</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>18.6801071034809</v>
+        <v>4.85</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>33.5696826454962</v>
+        <v>6.39</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="2" t="e">
+        <v>33.8</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>24.5826917154296</v>
+        <v>43.16</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>58.794932233353</v>
+        <v>31.3</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>32.7959921620912</v>
+        <v>76.81</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="2" t="e">
+        <v>33.65</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>21.5580176930344</v>
+        <v>26.91</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>73.9540365350619</v>
+        <v>21.56</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>47.0395733591903</v>
+        <v>73.95</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="2" t="e">
+        <v>47.04</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>31.3002761435947</v>
+        <v>26</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>76.8120212139069</v>
+        <v>24.58</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>33.6504858291417</v>
+        <v>58.79</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="2" t="e">
+        <v>32.8</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>19.2454959493773</v>
+        <v>20.22</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>70.3447259870359</v>
+        <v>19.25</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>50.1201947356726</v>
+        <v>70.34</v>
       </c>
       <c r="G29" s="2" t="n">
+        <v>50.12</v>
+      </c>
+      <c r="H29" s="2" t="n">
         <v>4.59547579213034e-289</v>
       </c>
-      <c r="H29" s="2" t="n">
+      <c r="I29" s="2" t="n">
         <v>36.3346308882382</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>21.9548591680657</v>
+        <v>19.53</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>52.0182675309369</v>
+        <v>21.95</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>32.4889400642385</v>
+        <v>52.02</v>
       </c>
       <c r="G30" s="2" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="H30" s="2" t="n">
         <v>1.35149418847058e-282</v>
       </c>
-      <c r="H30" s="2" t="n">
+      <c r="I30" s="2" t="n">
         <v>35.9226906426501</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>21.4045011433385</v>
+        <v>18.83</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>52.4012964054213</v>
+        <v>21.4</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>33.5696826454962</v>
+        <v>52.4</v>
       </c>
       <c r="G31" s="2" t="n">
+        <v>33.57</v>
+      </c>
+      <c r="H31" s="2" t="n">
         <v>2.58117745433273e-260</v>
       </c>
-      <c r="H31" s="2" t="n">
+      <c r="I31" s="2" t="n">
         <v>34.4661361288361</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>20.8097756702535</v>
+        <v>17.2</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>50.427224513848</v>
+        <v>20.81</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>33.2282891945943</v>
+        <v>50.43</v>
       </c>
       <c r="G32" s="2" t="n">
+        <v>33.23</v>
+      </c>
+      <c r="H32" s="2" t="n">
         <v>7.96562333925101e-219</v>
       </c>
-      <c r="H32" s="2" t="n">
+      <c r="I32" s="2" t="n">
         <v>31.5756811831133</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B33" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C33" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D33" t="n">
-        <v>20.8441478185638</v>
+        <v>17</v>
       </c>
       <c r="E33" t="n">
-        <v>49.6906305244549</v>
+        <v>20.84</v>
       </c>
       <c r="F33" t="n">
-        <v>32.688927943761</v>
+        <v>49.69</v>
       </c>
       <c r="G33" t="n">
+        <v>32.69</v>
+      </c>
+      <c r="H33" t="n">
         <v>3.30994748630371e-215</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>31.3109592863339</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>40</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>15.1251360174102</v>
+        <v>3.44</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>36.859163229228</v>
+        <v>15.13</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>33.4161565965699</v>
+        <v>36.86</v>
       </c>
       <c r="G34" s="2" t="n">
+        <v>33.42</v>
+      </c>
+      <c r="H34" s="2" t="n">
         <v>0.000000000126561958745311</v>
       </c>
-      <c r="H34" s="2" t="n">
+      <c r="I34" s="2" t="n">
         <v>6.4312462122369</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>14.7402872901388</v>
+        <v>2.5</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>35.8279316440778</v>
+        <v>14.74</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>33.3292931741511</v>
+        <v>35.83</v>
       </c>
       <c r="G35" s="2" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="H35" s="2" t="n">
         <v>0.00000288904839416641</v>
       </c>
-      <c r="H35" s="2" t="n">
+      <c r="I35" s="2" t="n">
         <v>4.67855417696457</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>14.6226132758724</v>
+        <v>2.24</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>35.9899823217443</v>
+        <v>14.62</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>33.7494697291073</v>
+        <v>35.99</v>
       </c>
       <c r="G36" s="2" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="H36" s="2" t="n">
         <v>0.0000285202907216257</v>
       </c>
-      <c r="H36" s="2" t="n">
+      <c r="I36" s="2" t="n">
         <v>4.18497068315479</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>13.0970443648722</v>
+        <v>-0.15</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>31.7913965822039</v>
+        <v>0</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>33.2848514231461</v>
+        <v>0</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.00482216141972397</v>
+        <v>0.15</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>-2.81867967510922</v>
+        <v>0.0000242523041990311</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>-4.22164762149319</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>32</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0</v>
+        <v>-1.49</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>0</v>
+        <v>13.1</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>0.145445730561784</v>
+        <v>31.79</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.0000242523041990311</v>
+        <v>33.28</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>-4.22164762149319</v>
+        <v>0.00482216141972397</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>-2.81867967510922</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>9.98972002176937</v>
+        <v>-7.82</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>24.3370654095463</v>
+        <v>8.8</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>33.4060561986142</v>
+        <v>14.01</v>
       </c>
       <c r="G39" s="2" t="n">
+        <v>21.83</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000070157924471246</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>-17.5406198784564</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>-9.07</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>24.34</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>33.41</v>
+      </c>
+      <c r="H40" s="2" t="n">
         <v>0.0000000000000000000000000000000000000000000000000000000000000000000349736437998169</v>
       </c>
-      <c r="H39" s="2" t="n">
+      <c r="I40" s="2" t="n">
         <v>-17.4490939449981</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>45</v>
-      </c>
-      <c r="B40" t="s">
-        <v>17</v>
-      </c>
-      <c r="C40" t="s">
-        <v>38</v>
-      </c>
-      <c r="D40" t="n">
-        <v>8.79903774981495</v>
-      </c>
-      <c r="E40" t="n">
-        <v>14.0100176782557</v>
-      </c>
-      <c r="F40" t="n">
-        <v>21.8330202209967</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000070157924471246</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-17.5406198784564</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>7.6889661164205</v>
+        <v>-12.26</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>15.6452563347083</v>
+        <v>7.69</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>27.9013393127689</v>
+        <v>15.65</v>
       </c>
       <c r="G41" s="2" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="H41" s="2" t="n">
         <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000511724486276993</v>
       </c>
-      <c r="H41" s="2" t="n">
+      <c r="I41" s="2" t="n">
         <v>-25.4626201627911</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>7.11793867433747</v>
+        <v>-15.87</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>17.1331761932823</v>
+        <v>7.12</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>33.0060804395693</v>
+        <v>17.13</v>
       </c>
       <c r="G42" s="2" t="n">
+        <v>33.01</v>
+      </c>
+      <c r="H42" s="2" t="n">
         <v>6.93607581871144e-217</v>
       </c>
-      <c r="H42" s="2" t="n">
+      <c r="I42" s="2" t="n">
         <v>-31.434043223085</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="D43" s="2" t="n">
-        <v>6.84358376666069</v>
+        <v>-16.93</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>16.8680023571008</v>
+        <v>6.84</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>33.7979516392946</v>
+        <v>16.87</v>
       </c>
       <c r="G43" s="2" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="H43" s="2" t="n">
         <v>2.15859448530577e-244</v>
       </c>
-      <c r="H43" s="2" t="n">
+      <c r="I43" s="2" t="n">
         <v>-33.3864184873774</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>6.53949293027791</v>
+        <v>-17.34</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>15.8073070123748</v>
+        <v>6.54</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>33.1454659313577</v>
+        <v>15.81</v>
       </c>
       <c r="G44" s="2" t="n">
+        <v>33.15</v>
+      </c>
+      <c r="H44" s="2" t="n">
         <v>6.46469629299199e-261</v>
       </c>
-      <c r="H44" s="2" t="n">
+      <c r="I44" s="2" t="n">
         <v>-34.5062482275266</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>4.870460120864</v>
+        <v>-19.7</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>11.9917501473188</v>
+        <v>5.64</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>33.7615902066541</v>
+        <v>13.74</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="2" t="e">
+        <v>33.44</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>5.63575958924796</v>
+        <v>-20.44</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>13.7448438420742</v>
+        <v>5.44</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>33.4424176312547</v>
+        <v>13.45</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="2" t="e">
+        <v>33.89</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>5.44132546635676</v>
+        <v>-21.77</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>13.450206246317</v>
+        <v>4.87</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>33.8949154596691</v>
+        <v>11.99</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="2" t="e">
+        <v>33.76</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>6.74371590952435</v>
+        <v>-26.91</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>26.0459634649381</v>
+        <v>6.74</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>52.9604266408096</v>
+        <v>26.05</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="2" t="e">
+        <v>52.96</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>2.4900036350418</v>
+        <v>-27.29</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>6.05480259281084</v>
+        <v>2.49</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>33.343433731289</v>
+        <v>6.05</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="2" t="e">
+        <v>33.34</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>40.749386484707</v>
+        <v>33.57</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>66.1099242571373</v>
+        <v>41.7</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>33.7494697291073</v>
+        <v>66.98</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="2" t="e">
+        <v>33.42</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>37.0260627683377</v>
+        <v>32.36</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>59.4581472130511</v>
+        <v>40.75</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>33.4060561986142</v>
+        <v>66.11</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="2" t="e">
+        <v>33.75</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>41.6999153669447</v>
+        <v>26.05</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>66.9838803651194</v>
+        <v>37.03</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>33.4161565965699</v>
+        <v>59.46</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="2" t="e">
+        <v>33.41</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>28.4853339436244</v>
+        <v>25.51</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>72.518935715673</v>
+        <v>36.88</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>52.9604266408096</v>
+        <v>58.52</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="2" t="e">
+        <v>33.01</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B54" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C54" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="D54" s="2" t="n">
-        <v>36.8810820735663</v>
+        <v>19.56</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>58.5162167411148</v>
+        <v>28.49</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>33.0060804395693</v>
+        <v>72.52</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="2" t="e">
+        <v>52.96</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>27.1713437178011</v>
+        <v>10.2</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>43.5327248009322</v>
+        <v>27.17</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>33.3292931741511</v>
+        <v>43.53</v>
       </c>
       <c r="G55" s="2" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="H55" s="2" t="n">
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000130315188877666</v>
       </c>
-      <c r="H55" s="2" t="n">
+      <c r="I55" s="2" t="n">
         <v>24.3167692996883</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>26.3408093612872</v>
+        <v>8.82</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>41.9693144299864</v>
+        <v>26.34</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>33.1454659313577</v>
+        <v>41.97</v>
       </c>
       <c r="G56" s="2" t="n">
+        <v>33.15</v>
+      </c>
+      <c r="H56" s="2" t="n">
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000010342364986513</v>
       </c>
-      <c r="H56" s="2" t="n">
+      <c r="I56" s="2" t="n">
         <v>21.0875775701569</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>26.1778831539911</v>
+        <v>8.59</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>41.813944455234</v>
+        <v>26.18</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>33.2282891945943</v>
+        <v>41.81</v>
       </c>
       <c r="G57" s="2" t="n">
+        <v>33.23</v>
+      </c>
+      <c r="H57" s="2" t="n">
         <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000163955941750188</v>
       </c>
-      <c r="H57" s="2" t="n">
+      <c r="I57" s="2" t="n">
         <v>20.5132523553922</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B58" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C58" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D58" t="n">
-        <v>25.9774109470026</v>
+        <v>6.94</v>
       </c>
       <c r="E58" t="n">
-        <v>34.841716838221</v>
+        <v>25.98</v>
       </c>
       <c r="F58" t="n">
-        <v>27.9013393127689</v>
+        <v>34.84</v>
       </c>
       <c r="G58" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="H58" t="n">
         <v>0.000000000000000000000000000000000000000000000000000000000000000000161253419152718</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>17.3615698174612</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B59" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C59" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D59" t="n">
-        <v>19.8984321470316</v>
+        <v>-0.15</v>
       </c>
       <c r="E59" t="n">
-        <v>47.941347834531</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>50.1201947356726</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>0.000000671947966015935</v>
+        <v>0.15</v>
       </c>
       <c r="H59" t="n">
-        <v>-4.96930069902352</v>
+        <v>0.0000000502596041634182</v>
+      </c>
+      <c r="I59" t="n">
+        <v>-5.45038956618829</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B60" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C60" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>-2.18</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>19.9</v>
       </c>
       <c r="F60" t="n">
-        <v>0.145445730561784</v>
+        <v>47.94</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0000000502596041634182</v>
+        <v>50.12</v>
       </c>
       <c r="H60" t="n">
-        <v>-5.45038956618829</v>
+        <v>0.000000671947966015935</v>
+      </c>
+      <c r="I60" t="n">
+        <v>-4.96930069902352</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>16.4045151739452</v>
+        <v>-4.62</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>17.216935327248</v>
+        <v>16.4</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>21.8330202209967</v>
+        <v>17.22</v>
       </c>
       <c r="G61" s="2" t="n">
+        <v>21.83</v>
+      </c>
+      <c r="H61" s="2" t="n">
         <v>0.0000000000000000000000000000000000000108211354156508</v>
       </c>
-      <c r="H61" s="2" t="n">
+      <c r="I61" s="2" t="n">
         <v>-13.0093836414052</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>15.7780719701528</v>
+        <v>-8.11</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>25.4612546125461</v>
+        <v>15.78</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>33.5696826454962</v>
+        <v>25.46</v>
       </c>
       <c r="G62" s="2" t="n">
+        <v>33.57</v>
+      </c>
+      <c r="H62" s="2" t="n">
         <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000023614276346955</v>
       </c>
-      <c r="H62" s="2" t="n">
+      <c r="I62" s="2" t="n">
         <v>-19.9272596818146</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>13.7162244032473</v>
+        <v>-11.36</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>21.9848514274616</v>
+        <v>13.72</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>33.343433731289</v>
+        <v>21.98</v>
       </c>
       <c r="G63" s="2" t="n">
+        <v>33.34</v>
+      </c>
+      <c r="H63" s="2" t="n">
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000242103794285498</v>
       </c>
-      <c r="H63" s="2" t="n">
+      <c r="I63" s="2" t="n">
         <v>-28.2312140911904</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>13.3785032337542</v>
+        <v>-11.7</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>21.0914740726355</v>
+        <v>13.38</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>32.7959921620912</v>
+        <v>21.09</v>
       </c>
       <c r="G64" s="2" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="H64" s="2" t="n">
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000019916163467183</v>
       </c>
-      <c r="H64" s="2" t="n">
+      <c r="I64" s="2" t="n">
         <v>-29.2777481573807</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D65" s="2" t="n">
-        <v>12.0542682194741</v>
+        <v>-14.15</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>19.4989318314236</v>
+        <v>12.05</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>33.6504858291417</v>
+        <v>19.5</v>
       </c>
       <c r="G65" s="2" t="n">
+        <v>33.65</v>
+      </c>
+      <c r="H65" s="2" t="n">
         <v>2.51519216692383e-274</v>
       </c>
-      <c r="H65" s="2" t="n">
+      <c r="I65" s="2" t="n">
         <v>-35.3890654057141</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D66" s="2" t="n">
-        <v>11.9717888948658</v>
+        <v>-14.35</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>19.4503787143135</v>
+        <v>11.97</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>33.7979516392946</v>
+        <v>19.45</v>
       </c>
       <c r="G66" s="2" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="H66" s="2" t="n">
         <v>1.76344838739284e-281</v>
       </c>
-      <c r="H66" s="2" t="n">
+      <c r="I66" s="2" t="n">
         <v>-35.8511700187167</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D67" s="2" t="n">
-        <v>11.7647058823529</v>
+        <v>-14.71</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>19.1687706350748</v>
+        <v>11.74</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>33.8949154596691</v>
+        <v>19.05</v>
       </c>
       <c r="G67" s="2" t="n">
+        <v>33.76</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>1.07588372062054e-296</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>-36.8146606979389</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>-14.73</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>19.17</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>33.89</v>
+      </c>
+      <c r="H68" s="2" t="n">
         <v>1.2728310046915e-296</v>
       </c>
-      <c r="H67" s="2" t="n">
+      <c r="I68" s="2" t="n">
         <v>-36.8100976297813</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>46</v>
-      </c>
-      <c r="B68" t="s">
-        <v>13</v>
-      </c>
-      <c r="C68" t="s">
-        <v>35</v>
-      </c>
-      <c r="D68" t="n">
-        <v>11.7393645665051</v>
-      </c>
-      <c r="E68" t="n">
-        <v>19.0522431540105</v>
-      </c>
-      <c r="F68" t="n">
-        <v>33.7615902066541</v>
-      </c>
-      <c r="G68" t="n">
-        <v>1.07588372062054e-296</v>
-      </c>
-      <c r="H68" t="n">
-        <v>-36.8146606979389</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D69" s="2" t="n">
-        <v>9.50071504072623</v>
+        <v>-17.65</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>14.8378325888522</v>
+        <v>9.5</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>32.4889400642385</v>
+        <v>14.84</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" s="2" t="e">
+        <v>32.49</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>9.11507097553609</v>
+        <v>-18.79</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>14.6533307438338</v>
+        <v>9.12</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>33.4424176312547</v>
+        <v>14.65</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" s="2" t="e">
+        <v>33.44</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>8.81226053639847</v>
+        <v>-18.84</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>13.8473489998058</v>
+        <v>8.81</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>32.688927943761</v>
+        <v>13.85</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" s="2" t="e">
+        <v>32.69</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D72" s="2" t="n">
-        <v>12.1532251138023</v>
+        <v>-19.56</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>27.4810642843271</v>
+        <v>12.15</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>47.0395733591903</v>
+        <v>27.48</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" s="2" t="e">
+        <v>47.04</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>31.8674086040807</v>
+        <v>40.58</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>54.5864507533053</v>
+        <v>43.7</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>33.7615902066541</v>
+        <v>73.93</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" s="2" t="e">
+        <v>33.34</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>38.9277389277389</v>
+        <v>34.73</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>66.7520754330225</v>
+        <v>40.18</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>33.7979516392946</v>
+        <v>68.18</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" s="2" t="e">
+        <v>33.44</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>40.1812141347025</v>
+        <v>32.95</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>68.1766936558368</v>
+        <v>38.93</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>33.4424176312547</v>
+        <v>66.75</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" s="2" t="e">
+        <v>33.8</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D76" s="2" t="n">
-        <v>32.4066029539531</v>
+        <v>20.82</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>45.8747565850159</v>
+        <v>31.87</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>27.9013393127689</v>
+        <v>54.59</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" s="2" t="e">
+        <v>33.76</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D77" s="2" t="n">
-        <v>30.6454496692294</v>
+        <v>18.81</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>52.7006251921697</v>
+        <v>30.65</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>33.8949154596691</v>
+        <v>52.7</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" s="2" t="e">
+        <v>33.89</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>43.6992608748334</v>
+        <v>17.97</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>73.9264118069079</v>
+        <v>32.41</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>33.343433731289</v>
+        <v>45.87</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" s="2" t="e">
+        <v>27.9</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>40</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>23.4675371780921</v>
+        <v>6.37</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>39.786819719176</v>
+        <v>23.47</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>33.4161565965699</v>
+        <v>39.79</v>
       </c>
       <c r="G79" s="2" t="n">
+        <v>33.42</v>
+      </c>
+      <c r="H79" s="2" t="n">
         <v>0.000000000000000000000000000000000000000000000000385103614173993</v>
       </c>
-      <c r="H79" s="2" t="n">
+      <c r="I79" s="2" t="n">
         <v>14.7348408321875</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D80" s="2" t="n">
-        <v>24.1117690599556</v>
+        <v>4.88</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>26.7090294147791</v>
+        <v>24.11</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>21.8330202209967</v>
+        <v>26.71</v>
       </c>
       <c r="G80" s="2" t="n">
+        <v>21.83</v>
+      </c>
+      <c r="H80" s="2" t="n">
         <v>0.000000000000000000000000000000000000218993138930086</v>
       </c>
-      <c r="H80" s="2" t="n">
+      <c r="I80" s="2" t="n">
         <v>12.7775010875897</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>22.4217393906746</v>
+        <v>4.69</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>38.3929486522497</v>
+        <v>21.67</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>33.7494697291073</v>
+        <v>51.73</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>0.00000000000000000000000000639745874121271</v>
+        <v>47.04</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>10.7429392643156</v>
+        <v>0.000000000000000000000000446586059401825</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>10.3437760642853</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>21.6739671905866</v>
+        <v>4.64</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>51.7269652557138</v>
+        <v>22.42</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>47.0395733591903</v>
+        <v>38.39</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>0.000000000000000000000000446586059401825</v>
+        <v>33.75</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>10.3437760642853</v>
+        <v>0.00000000000000000000000000639745874121271</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>10.7429392643156</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B83" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C83" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D83" t="n">
-        <v>20.5255811130667</v>
+        <v>1.38</v>
       </c>
       <c r="E83" t="n">
-        <v>34.6622937378293</v>
+        <v>20.53</v>
       </c>
       <c r="F83" t="n">
-        <v>33.2848514231461</v>
+        <v>34.66</v>
       </c>
       <c r="G83" t="n">
+        <v>33.28</v>
+      </c>
+      <c r="H83" t="n">
         <v>0.00130574660999238</v>
       </c>
-      <c r="H83" t="n">
+      <c r="I83" t="n">
         <v>3.21471374734926</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>20.3393910217836</v>
+        <v>1.07</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>34.6417956339039</v>
+        <v>20.34</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>33.5696826454962</v>
+        <v>34.64</v>
       </c>
       <c r="G84" s="2" t="n">
+        <v>33.57</v>
+      </c>
+      <c r="H84" s="2" t="n">
         <v>0.0124733230813737</v>
       </c>
-      <c r="H84" s="2" t="n">
+      <c r="I84" s="2" t="n">
         <v>2.4984628067184</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="E85" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>0.145445730561784</v>
+        <v>0</v>
       </c>
       <c r="G85" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H85" s="2" t="n">
         <v>0.000000134941883290294</v>
       </c>
-      <c r="H85" s="2" t="n">
+      <c r="I85" s="2" t="n">
         <v>-5.2720043439448</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>18.2532910775232</v>
+        <v>-2.45</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>30.6959106282669</v>
+        <v>18.25</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>33.1454659313577</v>
+        <v>30.7</v>
       </c>
       <c r="G86" s="2" t="n">
+        <v>33.15</v>
+      </c>
+      <c r="H86" s="2" t="n">
         <v>0.00000000823618320796703</v>
       </c>
-      <c r="H86" s="2" t="n">
+      <c r="I86" s="2" t="n">
         <v>-5.76355205973258</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D87" s="2" t="n">
-        <v>17.9654422702826</v>
+        <v>-4.69</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>48.2730347442862</v>
+        <v>17.97</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>52.9604266408096</v>
+        <v>48.27</v>
       </c>
       <c r="G87" s="2" t="n">
+        <v>52.96</v>
+      </c>
+      <c r="H87" s="2" t="n">
         <v>0.000000000000000000000000446586059401824</v>
       </c>
-      <c r="H87" s="2" t="n">
+      <c r="I87" s="2" t="n">
         <v>-10.3437760642853</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>16.756364515934</v>
+        <v>-5.01</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>28.4001229886236</v>
+        <v>16.76</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>33.4060561986142</v>
+        <v>28.4</v>
       </c>
       <c r="G88" s="2" t="n">
+        <v>33.41</v>
+      </c>
+      <c r="H88" s="2" t="n">
         <v>0.0000000000000000000000000000000301034652497753</v>
       </c>
-      <c r="H88" s="2" t="n">
+      <c r="I88" s="2" t="n">
         <v>-11.8218354329742</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>10.638944616694</v>
+        <v>-15.29</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>17.9358409347135</v>
+        <v>10.64</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>33.2282891945943</v>
+        <v>17.94</v>
       </c>
       <c r="G89" s="2" t="n">
+        <v>33.23</v>
+      </c>
+      <c r="H89" s="2" t="n">
         <v>1.10384236139509e-304</v>
       </c>
-      <c r="H89" s="2" t="n">
+      <c r="I89" s="2" t="n">
         <v>-37.3106227401187</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>10.673550246128</v>
+        <v>-15.43</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>18.222814389669</v>
+        <v>10.67</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>33.6504858291417</v>
+        <v>18.22</v>
       </c>
       <c r="G90" s="2" t="n">
+        <v>33.65</v>
+      </c>
+      <c r="H90" s="2" t="n">
         <v>1.14973861941767e-307</v>
       </c>
-      <c r="H90" s="2" t="n">
+      <c r="I90" s="2" t="n">
         <v>-37.4940903120439</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>4.2591556301685</v>
+        <v>-19.44</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>7.02060059444501</v>
+        <v>8.21</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>32.4889400642385</v>
+        <v>13.89</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H91" s="2" t="e">
+        <v>33.33</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>2.91345857714814</v>
+        <v>-22.7</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>4.847801578354</v>
+        <v>10.78</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>32.7959921620912</v>
+        <v>27.42</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" s="2" t="e">
+        <v>50.12</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>8.21261894660283</v>
+        <v>-25.16</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>13.8874654094496</v>
+        <v>4.69</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>33.3292931741511</v>
+        <v>7.85</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H93" s="2" t="e">
+        <v>33.01</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>10.7815082020072</v>
+        <v>-25.18</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>27.416214000205</v>
+        <v>4.53</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>50.1201947356726</v>
+        <v>7.51</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H94" s="2" t="e">
+        <v>32.69</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>4.52972438511927</v>
+        <v>-25.47</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>7.5125550886543</v>
+        <v>4.26</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>32.688927943761</v>
+        <v>7.02</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" s="2" t="e">
+        <v>32.49</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>4.68816941061264</v>
+        <v>-27.95</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>7.85077380342318</v>
+        <v>2.91</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>33.0060804395693</v>
+        <v>4.85</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" s="2" t="e">
+        <v>32.8</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>45.5274337342189</v>
+        <v>45.66</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>76.3802449307368</v>
+        <v>47.23</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>33.7615902066541</v>
+        <v>79.55</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="2" t="e">
+        <v>33.89</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>37.4095989480605</v>
+        <v>42.62</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>62.8287492471391</v>
+        <v>45.53</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>33.7979516392946</v>
+        <v>76.38</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" s="2" t="e">
+        <v>33.76</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>32.2983992751435</v>
+        <v>33.37</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>53.6739610519976</v>
+        <v>40.08</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>33.4424176312547</v>
+        <v>67.02</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H99" s="2" t="e">
+        <v>33.65</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>44.0969652109548</v>
+        <v>29.03</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>47.8417988355752</v>
+        <v>37.41</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>21.8330202209967</v>
+        <v>62.83</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H100" s="2" t="e">
+        <v>33.8</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>47.2316586208952</v>
+        <v>26.01</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>79.5522987351937</v>
+        <v>44.1</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>33.8949154596691</v>
+        <v>47.84</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" s="2" t="e">
+        <v>21.83</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>29.9450313493086</v>
+        <v>22.96</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>69.9959847420197</v>
+        <v>29.95</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>47.0395733591903</v>
+        <v>70</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H102" s="2" t="e">
+        <v>47.04</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>40.0828430784008</v>
+        <v>20.23</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>67.024693836579</v>
+        <v>32.3</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>33.6504858291417</v>
+        <v>53.67</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H103" s="2" t="e">
+        <v>33.44</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>28.2043567216271</v>
+        <v>13.48</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>47.048785384461</v>
+        <v>28.2</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>33.5696826454962</v>
+        <v>47.05</v>
       </c>
       <c r="G104" s="2" t="n">
+        <v>33.57</v>
+      </c>
+      <c r="H104" s="2" t="n">
         <v>4.36209033733548e-215</v>
       </c>
-      <c r="H104" s="2" t="n">
+      <c r="I104" s="2" t="n">
         <v>31.3021516010409</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B105" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C105" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D105" t="n">
-        <v>100</v>
+        <v>5.97</v>
       </c>
       <c r="E105" t="n">
-        <v>0.722746436458542</v>
+        <v>24.43</v>
       </c>
       <c r="F105" t="n">
-        <v>0.145445730561784</v>
+        <v>33.87</v>
       </c>
       <c r="G105" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000600094310970047</v>
+        <v>27.9</v>
       </c>
       <c r="H105" t="n">
-        <v>15.0133808003726</v>
+        <v>0.00000000000000000000000000000000000000000000000144158552309114</v>
+      </c>
+      <c r="I105" t="n">
+        <v>14.6453961621452</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>24.4280335939763</v>
+        <v>0.58</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>33.8687010640434</v>
+        <v>100</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>27.9013393127689</v>
+        <v>0.72</v>
       </c>
       <c r="G106" s="2" t="n">
-        <v>0.00000000000000000000000000000000000000000000000144158552309114</v>
+        <v>0.15</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>14.6453961621452</v>
+        <v>0.00000000000000000000000000000000000000000000000000600094310970047</v>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>15.0133808003726</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D107" s="2" t="n">
-        <v>18.5825724133761</v>
+        <v>-2.56</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>30.8472194338486</v>
+        <v>18.58</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>33.4060561986142</v>
+        <v>30.85</v>
       </c>
       <c r="G107" s="2" t="n">
+        <v>33.41</v>
+      </c>
+      <c r="H107" s="2" t="n">
         <v>0.00000000114299157526037</v>
       </c>
-      <c r="H107" s="2" t="n">
+      <c r="I107" s="2" t="n">
         <v>-6.08804302750859</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D108" s="2" t="n">
-        <v>16.9655425668646</v>
+        <v>-5.18</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>27.8257378036539</v>
+        <v>16.97</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>33.0060804395693</v>
+        <v>27.83</v>
       </c>
       <c r="G108" s="2" t="n">
+        <v>33.01</v>
+      </c>
+      <c r="H108" s="2" t="n">
         <v>0.000000000000000000000000000000000016008959678034</v>
       </c>
-      <c r="H108" s="2" t="n">
+      <c r="I108" s="2" t="n">
         <v>-12.4392048623555</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B109" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C109" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D109" t="n">
-        <v>14.3705679132069</v>
+        <v>-9.53</v>
       </c>
       <c r="E109" t="n">
-        <v>23.8004416783778</v>
+        <v>14.37</v>
       </c>
       <c r="F109" t="n">
-        <v>33.3292931741511</v>
+        <v>23.8</v>
       </c>
       <c r="G109" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="H109" t="n">
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000752321262938645</v>
       </c>
-      <c r="H109" t="n">
+      <c r="I109" t="n">
         <v>-23.0790148792663</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>13.6421666970637</v>
+        <v>-10.7</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>22.5255972696246</v>
+        <v>13.64</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>33.2282891945943</v>
+        <v>22.53</v>
       </c>
       <c r="G110" s="2" t="n">
+        <v>33.23</v>
+      </c>
+      <c r="H110" s="2" t="n">
         <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000191629585225962</v>
       </c>
-      <c r="H110" s="2" t="n">
+      <c r="I110" s="2" t="n">
         <v>-26.0364370331936</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>12.2927840078011</v>
+        <v>-12.9</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>20.24693836579</v>
+        <v>12.29</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>33.1454659313577</v>
+        <v>20.25</v>
       </c>
       <c r="G111" s="2" t="n">
+        <v>33.15</v>
+      </c>
+      <c r="H111" s="2" t="n">
         <v>1.62051459649029e-219</v>
       </c>
-      <c r="H111" s="2" t="n">
+      <c r="I111" s="2" t="n">
         <v>-31.6260216499758</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="s">
-        <v>48</v>
-      </c>
-      <c r="B112" t="s">
-        <v>13</v>
-      </c>
-      <c r="C112" t="s">
-        <v>34</v>
-      </c>
-      <c r="D112" t="n">
-        <v>11.0851738792123</v>
-      </c>
-      <c r="E112" t="n">
-        <v>18.5906444489058</v>
-      </c>
-      <c r="F112" t="n">
-        <v>33.7494697291073</v>
-      </c>
-      <c r="G112" t="n">
+      <c r="A112" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>-15.16</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="F112" s="2" t="n">
+        <v>18.59</v>
+      </c>
+      <c r="G112" s="2" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="H112" s="2" t="n">
         <v>1.7029667396973e-303</v>
       </c>
-      <c r="H112" t="n">
+      <c r="I112" s="2" t="n">
         <v>-37.2372686957989</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>3.11509046819623</v>
+        <v>-18.87</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>5.02911062035736</v>
+        <v>8.76</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>32.4889400642385</v>
+        <v>14.55</v>
       </c>
       <c r="G113" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H113" s="2" t="e">
+        <v>33.42</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>3.8805050816138</v>
+        <v>-22.96</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>6.32403131901225</v>
+        <v>11.4</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>32.7959921620912</v>
+        <v>30</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H114" s="2" t="e">
+        <v>52.96</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D115" s="2" t="n">
-        <v>7.05332312280843</v>
+        <v>-26.47</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>17.5667536639229</v>
+        <v>3.88</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>50.1201947356726</v>
+        <v>6.32</v>
       </c>
       <c r="G115" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H115" s="2" t="e">
+        <v>32.8</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="s">
-        <v>48</v>
-      </c>
-      <c r="B116" t="s">
-        <v>19</v>
-      </c>
-      <c r="C116" t="s">
-        <v>20</v>
-      </c>
-      <c r="D116" t="n">
-        <v>3.63366703744902</v>
-      </c>
-      <c r="E116" t="n">
-        <v>5.9024292310781</v>
-      </c>
-      <c r="F116" t="n">
-        <v>32.688927943761</v>
-      </c>
-      <c r="G116" t="n">
-        <v>0</v>
-      </c>
-      <c r="H116" t="e">
+      <c r="A116" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>-26.79</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="G116" s="2" t="n">
+        <v>32.69</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>8.759521218716</v>
+        <v>-27.46</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>14.5452720337282</v>
+        <v>3.12</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>33.4161565965699</v>
+        <v>5.03</v>
       </c>
       <c r="G117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H117" s="2" t="e">
+        <v>32.49</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>11.4009993515658</v>
+        <v>-28.19</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>30.0040152579803</v>
+        <v>3.11</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>52.9604266408096</v>
+        <v>5.15</v>
       </c>
       <c r="G118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H118" s="2" t="e">
+        <v>33.34</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" s="2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B119" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C119" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D119" t="n">
-        <v>3.10796074154853</v>
+        <v>-32.55</v>
       </c>
       <c r="E119" t="n">
-        <v>5.14956835976712</v>
+        <v>7.05</v>
       </c>
       <c r="F119" t="n">
-        <v>33.343433731289</v>
+        <v>17.57</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
-      </c>
-      <c r="H119" t="e">
+        <v>50.12</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="e">
         <v>#NUM!</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:I1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>

--- a/output/tables/2025/tabla6_v_test.xlsx
+++ b/output/tables/2025/tabla6_v_test.xlsx
@@ -57,19 +57,19 @@
     <t xml:space="preserve">1</t>
   </si>
   <si>
-    <t xml:space="preserve">comper_pct_rec_tercil</t>
+    <t xml:space="preserve">comper_pct_cat</t>
   </si>
   <si>
     <t xml:space="preserve">Bajas prácticas de evitación</t>
   </si>
   <si>
-    <t xml:space="preserve">emper_ep_pct_rec_tercil</t>
+    <t xml:space="preserve">emper_ep_pct_cat</t>
   </si>
   <si>
     <t xml:space="preserve">Baja inseguridad en espacio publico</t>
   </si>
   <si>
-    <t xml:space="preserve">emper_barrio_pct_rec_tercil</t>
+    <t xml:space="preserve">emper_barrio_pct_cat</t>
   </si>
   <si>
     <t xml:space="preserve">Baja inseguridad en el barrio</t>
@@ -87,19 +87,19 @@
     <t xml:space="preserve">No gasta en medidas de seguridad</t>
   </si>
   <si>
-    <t xml:space="preserve">comgen_per_pct_rec_tercil</t>
+    <t xml:space="preserve">comgen_per_pct_cat</t>
   </si>
   <si>
     <t xml:space="preserve">Media disposición de medidas vivienda</t>
   </si>
   <si>
-    <t xml:space="preserve">comgen_com_pct_rec_tercil</t>
+    <t xml:space="preserve">comgen_com_pct_cat</t>
   </si>
   <si>
     <t xml:space="preserve">Baja adopción de medidas comunitarias</t>
   </si>
   <si>
-    <t xml:space="preserve">emper_casa_pct_rec_tercil</t>
+    <t xml:space="preserve">emper_casa_pct_cat</t>
   </si>
   <si>
     <t xml:space="preserve">Baja inseguridad en la casa</t>
@@ -544,7 +544,7 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="7.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="27.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="20.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="45.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="7.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="7.71" hidden="0" customWidth="1"/>

--- a/output/tables/2025/tabla6_v_test.xlsx
+++ b/output/tables/2025/tabla6_v_test.xlsx
@@ -57,28 +57,40 @@
     <t xml:space="preserve">1</t>
   </si>
   <si>
+    <t xml:space="preserve">emper_barrio_pct_cat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sin inseguridad en el barrio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emper_ep_pct_cat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sin inseguridad en espacio público</t>
+  </si>
+  <si>
+    <t xml:space="preserve">perper_delito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No cree que será victima de delito</t>
+  </si>
+  <si>
     <t xml:space="preserve">comper_pct_cat</t>
   </si>
   <si>
-    <t xml:space="preserve">Bajas prácticas de evitación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">emper_ep_pct_cat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baja inseguridad en espacio publico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">emper_barrio_pct_cat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baja inseguridad en el barrio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">perper_delito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No cree que será victima de delito</t>
+    <t xml:space="preserve">No modificó prácticas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emper_casa_pct_cat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sin inseguridad en la casa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comgen_per_pct_cat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Una o dos medidas en la vivienda</t>
   </si>
   <si>
     <t xml:space="preserve">comper_gasto</t>
@@ -87,70 +99,58 @@
     <t xml:space="preserve">No gasta en medidas de seguridad</t>
   </si>
   <si>
-    <t xml:space="preserve">comgen_per_pct_cat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Media disposición de medidas vivienda</t>
-  </si>
-  <si>
     <t xml:space="preserve">comgen_com_pct_cat</t>
   </si>
   <si>
-    <t xml:space="preserve">Baja adopción de medidas comunitarias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">emper_casa_pct_cat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baja inseguridad en la casa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baja disposición de medidas vivienda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Media inseguridad en la casa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Media adopción de medidas comunitarias</t>
+    <t xml:space="preserve">Sin medidas en el barrio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Una medida en el barrio</t>
   </si>
   <si>
     <t xml:space="preserve">Cree que será victima de otro tipo de delito</t>
   </si>
   <si>
-    <t xml:space="preserve">Media inseguridad en el barrio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alta adopción de medidas comunitarias</t>
+    <t xml:space="preserve">Modificó hasta la mitad de las prácticas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sin medidas en la vivienda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gasta en medidas de seguridad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dos o más medidas en el barrio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tres o más medidas en la vivienda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inseguridad en la casa, de día y de noche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inseguridad en hasta la mitad de los lugares</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inseguridad en la casa, de día o de noche</t>
   </si>
   <si>
     <t xml:space="preserve">Cree que será victima de delito no violento</t>
   </si>
   <si>
-    <t xml:space="preserve">Alta inseguridad en la casa</t>
+    <t xml:space="preserve">Inseguridad en el barrio, de día y de noche</t>
   </si>
   <si>
     <t xml:space="preserve">Cree que será victima de delito violento</t>
   </si>
   <si>
-    <t xml:space="preserve">Media inseguridad en espacio publico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medias prácticas de evitación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gasta en medidas de seguridad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alta inseguridad en espacio publico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alta disposición de medidas vivienda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Altas prácticas de evitación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alta inseguridad en el barrio</t>
+    <t xml:space="preserve">Modificó más de la mitad de las prácticas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inseguridad en el barrio, de día o de noche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inseguridad en más de la mitad de los lugares</t>
   </si>
   <si>
     <t xml:space="preserve">2</t>
@@ -545,7 +545,7 @@
   <cols>
     <col min="1" max="1" width="7.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="20.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="45.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="46.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="7.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="7.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="7.71" hidden="0" customWidth="1"/>
@@ -594,16 +594,16 @@
         <v>15</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>46.55</v>
+        <v>51.14</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>62.18</v>
+        <v>61.18</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>79.24</v>
+        <v>87.59</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>32.69</v>
+        <v>36.45</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>0</v>
@@ -623,16 +623,16 @@
         <v>17</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>44.99</v>
+        <v>40.38</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>61.17</v>
+        <v>73.75</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>77.48</v>
+        <v>61.67</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>32.49</v>
+        <v>21.29</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>0</v>
@@ -652,16 +652,16 @@
         <v>19</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>37.84</v>
+        <v>38.1</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>55.24</v>
+        <v>44.81</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>70.63</v>
+        <v>88.22</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>32.8</v>
+        <v>50.12</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>0</v>
@@ -681,16 +681,16 @@
         <v>21</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>33.94</v>
+        <v>33.12</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>43.02</v>
+        <v>75.52</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>84.06</v>
+        <v>49.96</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>50.12</v>
+        <v>16.84</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>0</v>
@@ -710,16 +710,16 @@
         <v>23</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>20.14</v>
+        <v>22.89</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>35.4</v>
+        <v>33.16</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>73.1</v>
+        <v>98.57</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>52.96</v>
+        <v>75.68</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>0</v>
@@ -739,22 +739,22 @@
         <v>25</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>14.74</v>
+        <v>12.54</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>36.99</v>
+        <v>31.46</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>48.08</v>
+        <v>65.76</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>33.34</v>
+        <v>53.21</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2" t="e">
-        <v>#NUM!</v>
+        <v>4.47026742593895e-238</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>32.9483278177001</v>
       </c>
     </row>
     <row r="8">
@@ -768,51 +768,51 @@
         <v>27</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>14.11</v>
+        <v>5.93</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>36.57</v>
+        <v>28.31</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>47.26</v>
+        <v>58.89</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>33.15</v>
+        <v>52.96</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2" t="e">
-        <v>#NUM!</v>
+        <v>0.00000000000000000000000000000000000000000000000000000368276649425945</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>15.4961560094703</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
+      <c r="A9" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="2" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>35.51</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>46.13</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>7.6261156470751e-268</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>34.9651331267459</v>
+      <c r="D9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>29.55</v>
+      </c>
+      <c r="F9" t="n">
+        <v>36.88</v>
+      </c>
+      <c r="G9" t="n">
+        <v>31.78</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.00000000000000000000000000000000000000000000252089109607374</v>
+      </c>
+      <c r="I9" t="n">
+        <v>14.1288892456039</v>
       </c>
     </row>
     <row r="10">
@@ -820,28 +820,28 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>11.19</v>
+        <v>2.83</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>34.35</v>
+        <v>27.95</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>44.2</v>
+        <v>31.8</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>33.01</v>
+        <v>28.97</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1.88578809537332e-206</v>
+        <v>0.000000000000000708378733105169</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>30.6609960606726</v>
+        <v>8.06906616238314</v>
       </c>
     </row>
     <row r="11">
@@ -849,28 +849,28 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>3.99</v>
+        <v>-0.1</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>28.73</v>
+        <v>8.33</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>37.22</v>
+        <v>0.05</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>33.23</v>
+        <v>0.15</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.000000000000000000000000000362635385359878</v>
+        <v>0.000264561533330723</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>11.0047213221523</v>
+        <v>-3.64773574302505</v>
       </c>
     </row>
     <row r="12">
@@ -878,28 +878,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>32</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.78</v>
+        <v>-3.52</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>26.25</v>
+        <v>23.63</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>34.06</v>
+        <v>45.46</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>33.28</v>
+        <v>48.98</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0.0316493765074051</v>
+        <v>0.0000000000000000000521964346166486</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>2.14881110802096</v>
+        <v>-9.15937979286482</v>
       </c>
     </row>
     <row r="13">
@@ -907,28 +907,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>-0.15</v>
+        <v>-4.43</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0</v>
+        <v>14.96</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0</v>
+        <v>6.31</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.15</v>
+        <v>10.73</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.00000000052975689348314</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000479453643159562</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>-6.21002643377842</v>
+        <v>-19.5423274064729</v>
       </c>
     </row>
     <row r="14">
@@ -936,28 +936,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>-10.43</v>
+        <v>-5.93</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>17.65</v>
+        <v>22.25</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>22.98</v>
+        <v>41.11</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>33.41</v>
+        <v>47.04</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000115108479305011</v>
+        <v>0.00000000000000000000000000000000000000000000000000000368276649425944</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>-29.5310234109178</v>
+        <v>-15.4961560094703</v>
       </c>
     </row>
     <row r="15">
@@ -965,28 +965,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>-14.89</v>
+        <v>-7.93</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>14.27</v>
+        <v>20.32</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>18.68</v>
+        <v>31.32</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>33.57</v>
+        <v>39.26</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="2" t="e">
-        <v>#NUM!</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000054611995782411</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>-21.3342511290279</v>
       </c>
     </row>
     <row r="16">
@@ -994,28 +994,28 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>-16.23</v>
+        <v>-8.12</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>6.59</v>
+        <v>19.73</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>5.61</v>
+        <v>27.94</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>21.83</v>
+        <v>36.05</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="2" t="e">
-        <v>#NUM!</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000564899329389252</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>-22.2809942865159</v>
       </c>
     </row>
     <row r="17">
@@ -1023,22 +1023,22 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>-16.79</v>
+        <v>-8.56</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>12.77</v>
+        <v>0.98</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>16.65</v>
+        <v>0.34</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>33.44</v>
+        <v>8.9</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>0</v>
@@ -1052,28 +1052,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>-17.57</v>
+        <v>-9.55</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>9.5</v>
+        <v>19.8</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>10.33</v>
+        <v>33.43</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>27.9</v>
+        <v>42.98</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="2" t="e">
-        <v>#NUM!</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000303717993837805</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>-25.3019895784166</v>
       </c>
     </row>
     <row r="19">
@@ -1081,22 +1081,22 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>-19.12</v>
+        <v>-14.33</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>11.12</v>
+        <v>1.8</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>14.63</v>
+        <v>1.09</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>33.75</v>
+        <v>15.41</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>0</v>
@@ -1110,22 +1110,22 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>40</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>-19.15</v>
+        <v>-16.53</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>10.95</v>
+        <v>6.19</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>14.26</v>
+        <v>5.31</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>33.42</v>
+        <v>21.83</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>0</v>
@@ -1139,22 +1139,22 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>41</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>-20.14</v>
+        <v>-20.58</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>14.67</v>
+        <v>0.95</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>26.9</v>
+        <v>0.79</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>47.04</v>
+        <v>21.37</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>0</v>
@@ -1168,22 +1168,22 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>42</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>-25.87</v>
+        <v>-21.47</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>6</v>
+        <v>5.86</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>7.89</v>
+        <v>6.43</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>33.76</v>
+        <v>27.9</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>-25.92</v>
+        <v>-29.6</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>5.89</v>
+        <v>3.41</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>7.73</v>
+        <v>4.58</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>33.65</v>
+        <v>34.18</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>0</v>
@@ -1232,16 +1232,16 @@
         <v>44</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>-27.4</v>
+        <v>-30.57</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>4.92</v>
+        <v>7.01</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>6.5</v>
+        <v>11.62</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>33.89</v>
+        <v>42.18</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>0</v>
@@ -1255,22 +1255,22 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>-27.41</v>
+        <v>-30.83</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>4.85</v>
+        <v>3.49</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>6.39</v>
+        <v>4.9</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>33.8</v>
+        <v>35.73</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>0</v>
@@ -1287,19 +1287,19 @@
         <v>24</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>43.16</v>
+        <v>89.27</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>31.3</v>
+        <v>69.08</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>76.81</v>
+        <v>100</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>33.65</v>
+        <v>10.73</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>0</v>
@@ -1313,22 +1313,22 @@
         <v>46</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>26.91</v>
+        <v>37.18</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>21.56</v>
+        <v>12.62</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>73.95</v>
+        <v>90.14</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>47.04</v>
+        <v>52.96</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>0</v>
@@ -1342,22 +1342,22 @@
         <v>46</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>26</v>
+        <v>33.62</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>24.58</v>
+        <v>15.26</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>58.79</v>
+        <v>65.4</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>32.8</v>
+        <v>31.78</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>0</v>
@@ -1371,28 +1371,28 @@
         <v>46</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>20.22</v>
+        <v>8.44</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>19.25</v>
+        <v>8.66</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>70.34</v>
+        <v>58.56</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>50.12</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>4.59547579213034e-289</v>
+        <v>0.0000000000000000000000000183550413023622</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>36.3346308882382</v>
+        <v>10.6452198779529</v>
       </c>
     </row>
     <row r="30">
@@ -1400,28 +1400,28 @@
         <v>46</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>19.53</v>
+        <v>8.39</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>21.95</v>
+        <v>11.11</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>52.02</v>
+        <v>25.23</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>32.49</v>
+        <v>16.84</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>1.35149418847058e-282</v>
+        <v>0.0000000000000000000000000000000000000000517430012116881</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>35.9226906426501</v>
+        <v>13.4115541561867</v>
       </c>
     </row>
     <row r="31">
@@ -1429,28 +1429,28 @@
         <v>46</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>18.83</v>
+        <v>7.97</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>21.4</v>
+        <v>10.19</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>52.4</v>
+        <v>29.26</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>33.57</v>
+        <v>21.29</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>2.58117745433273e-260</v>
+        <v>0.0000000000000000000000000000000276163061804652</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>34.4661361288361</v>
+        <v>11.829076592308</v>
       </c>
     </row>
     <row r="32">
@@ -1458,57 +1458,57 @@
         <v>46</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>17.2</v>
+        <v>7.34</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>20.81</v>
+        <v>8.91</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>50.43</v>
+        <v>43.79</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>33.23</v>
+        <v>36.45</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>7.96562333925101e-219</v>
+        <v>0.00000000000000000000227250109476776</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>31.5756811831133</v>
+        <v>9.49172136928217</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="s">
+      <c r="A33" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B33" t="s">
-        <v>14</v>
-      </c>
-      <c r="C33" t="s">
-        <v>15</v>
-      </c>
-      <c r="D33" t="n">
-        <v>17</v>
-      </c>
-      <c r="E33" t="n">
-        <v>20.84</v>
-      </c>
-      <c r="F33" t="n">
-        <v>49.69</v>
-      </c>
-      <c r="G33" t="n">
-        <v>32.69</v>
-      </c>
-      <c r="H33" t="n">
-        <v>3.30994748630371e-215</v>
-      </c>
-      <c r="I33" t="n">
-        <v>31.3109592863339</v>
+      <c r="B33" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>77.55</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>75.68</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>0.0058365163286521</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>2.75682732879425</v>
       </c>
     </row>
     <row r="34">
@@ -1516,28 +1516,28 @@
         <v>46</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>3.44</v>
+        <v>-0.15</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>15.13</v>
+        <v>0</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>36.86</v>
+        <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>33.42</v>
+        <v>0.15</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>0.000000000126561958745311</v>
+        <v>0.00388659940235587</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>6.4312462122369</v>
+        <v>-2.88722196349525</v>
       </c>
     </row>
     <row r="35">
@@ -1545,28 +1545,28 @@
         <v>46</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>2.5</v>
+        <v>-1.66</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>14.74</v>
+        <v>6.03</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>35.83</v>
+        <v>7.25</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>33.33</v>
+        <v>8.9</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>0.00000288904839416641</v>
+        <v>0.000172967722370407</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>4.67855417696457</v>
+        <v>-3.75554059281194</v>
       </c>
     </row>
     <row r="36">
@@ -1577,25 +1577,25 @@
         <v>16</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>2.24</v>
+        <v>-2.32</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>14.62</v>
+        <v>7.01</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>35.99</v>
+        <v>40.65</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>33.75</v>
+        <v>42.98</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>0.0000285202907216257</v>
+        <v>0.00310146478703029</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>4.18497068315479</v>
+        <v>-2.95749828063604</v>
       </c>
     </row>
     <row r="37">
@@ -1603,57 +1603,57 @@
         <v>46</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>-0.15</v>
+        <v>-3.08</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>0</v>
+        <v>24.82</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.15</v>
+        <v>27.9</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>0.0000242523041990311</v>
+        <v>0.0000126653226366557</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>-4.22164762149319</v>
+        <v>-4.36580881091649</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="s">
+      <c r="A38" t="s">
         <v>46</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D38" s="2" t="n">
-        <v>-1.49</v>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>31.79</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>33.28</v>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>0.00482216141972397</v>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>-2.81867967510922</v>
+      <c r="B38" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38" t="s">
+        <v>44</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-3.57</v>
+      </c>
+      <c r="E38" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="F38" t="n">
+        <v>38.61</v>
+      </c>
+      <c r="G38" t="n">
+        <v>42.18</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.00000490230712336264</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-4.56892561704316</v>
       </c>
     </row>
     <row r="39">
@@ -1661,28 +1661,28 @@
         <v>46</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>-7.82</v>
+        <v>-3.77</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>8.8</v>
+        <v>6.11</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>14.01</v>
+        <v>17.6</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>21.83</v>
+        <v>21.37</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000070157924471246</v>
+        <v>0.0000000035350545869592</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>-17.5406198784564</v>
+        <v>-5.90459903731453</v>
       </c>
     </row>
     <row r="40">
@@ -1690,28 +1690,28 @@
         <v>46</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>-9.07</v>
+        <v>-4.65</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>9.99</v>
+        <v>6.54</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>24.34</v>
+        <v>34.6</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>33.41</v>
+        <v>39.26</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000349736437998169</v>
+        <v>0.00000000155628385568802</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>-17.4490939449981</v>
+        <v>-6.03842224670924</v>
       </c>
     </row>
     <row r="41">
@@ -1719,28 +1719,28 @@
         <v>46</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>-12.26</v>
+        <v>-5.21</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>7.69</v>
+        <v>5.64</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>15.65</v>
+        <v>16.62</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>27.9</v>
+        <v>21.83</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000511724486276993</v>
+        <v>0.000000000000000294118341320214</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>-25.4626201627911</v>
+        <v>-8.17571423091445</v>
       </c>
     </row>
     <row r="42">
@@ -1748,28 +1748,28 @@
         <v>46</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>-15.87</v>
+        <v>-5.65</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>7.12</v>
+        <v>6.24</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>17.13</v>
+        <v>30.08</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>33.01</v>
+        <v>35.73</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>6.93607581871144e-217</v>
+        <v>0.0000000000000577536678724439</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>-31.434043223085</v>
+        <v>-7.51307669793077</v>
       </c>
     </row>
     <row r="43">
@@ -1777,28 +1777,28 @@
         <v>46</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>-16.93</v>
+        <v>-9.19</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>6.84</v>
+        <v>5.42</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>16.87</v>
+        <v>24.99</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>33.8</v>
+        <v>34.18</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>2.15859448530577e-244</v>
+        <v>0.0000000000000000000000000000000000083073066371863</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>-33.3864184873774</v>
+        <v>-12.4914994329822</v>
       </c>
     </row>
     <row r="44">
@@ -1806,28 +1806,28 @@
         <v>46</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>-17.34</v>
+        <v>-28.97</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>6.54</v>
+        <v>0</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>15.81</v>
+        <v>0</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>33.15</v>
+        <v>28.97</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>6.46469629299199e-261</v>
-      </c>
-      <c r="I44" s="2" t="n">
-        <v>-34.5062482275266</v>
+        <v>0</v>
+      </c>
+      <c r="I44" s="2" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="45">
@@ -1835,22 +1835,22 @@
         <v>46</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>-19.7</v>
+        <v>-36.05</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>13.74</v>
+        <v>0</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>33.44</v>
+        <v>36.05</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>0</v>
@@ -1864,22 +1864,22 @@
         <v>46</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>-20.44</v>
+        <v>-37.18</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>5.44</v>
+        <v>1.55</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>13.45</v>
+        <v>9.86</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>33.89</v>
+        <v>47.04</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>0</v>
@@ -1893,22 +1893,22 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>-21.77</v>
+        <v>-53.21</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>4.87</v>
+        <v>0</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>11.99</v>
+        <v>0</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>33.76</v>
+        <v>53.21</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>0</v>
@@ -1919,25 +1919,25 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>-26.91</v>
+        <v>28.98</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>6.74</v>
+        <v>53.66</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>26.05</v>
+        <v>71.95</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>52.96</v>
+        <v>42.98</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>0</v>
@@ -1948,25 +1948,25 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>-27.29</v>
+        <v>25.76</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>2.49</v>
+        <v>48.91</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>6.05</v>
+        <v>74.74</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>33.34</v>
+        <v>48.98</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>0</v>
@@ -1983,19 +1983,19 @@
         <v>14</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>33.57</v>
+        <v>22.43</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>41.7</v>
+        <v>49.09</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>66.98</v>
+        <v>64.61</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>33.42</v>
+        <v>42.18</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>0</v>
@@ -2009,22 +2009,22 @@
         <v>47</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>32.36</v>
+        <v>17.98</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>40.75</v>
+        <v>39.66</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>66.11</v>
+        <v>93.66</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>33.75</v>
+        <v>75.68</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>0</v>
@@ -2038,22 +2038,22 @@
         <v>47</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>26.05</v>
+        <v>15.33</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>37.03</v>
+        <v>45.68</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>59.46</v>
+        <v>51.39</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>33.41</v>
+        <v>36.05</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>0</v>
@@ -2067,22 +2067,22 @@
         <v>47</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>25.51</v>
+        <v>11.75</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>36.88</v>
+        <v>45.55</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>58.52</v>
+        <v>39.65</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>33.01</v>
+        <v>27.9</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>0</v>
@@ -2096,28 +2096,28 @@
         <v>47</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>19.56</v>
+        <v>10.45</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>28.49</v>
+        <v>39.17</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>72.52</v>
+        <v>57.49</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>52.96</v>
+        <v>47.04</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="2" t="e">
-        <v>#NUM!</v>
+        <v>9.72367944656561e-225</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>32.0035769510696</v>
       </c>
     </row>
     <row r="55">
@@ -2128,25 +2128,25 @@
         <v>28</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>10.2</v>
+        <v>10.34</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>27.17</v>
+        <v>40.49</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>43.53</v>
+        <v>49.6</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>33.33</v>
+        <v>39.26</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000130315188877666</v>
+        <v>2.35365962455303e-227</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>24.3167692996883</v>
+        <v>32.1910671357744</v>
       </c>
     </row>
     <row r="56">
@@ -2154,28 +2154,28 @@
         <v>47</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>8.82</v>
+        <v>-0.15</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>26.34</v>
+        <v>0</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>41.97</v>
+        <v>0</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>33.15</v>
+        <v>0.15</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000010342364986513</v>
+        <v>0.000000000000806832474914543</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>21.0875775701569</v>
+        <v>-7.1599894882969</v>
       </c>
     </row>
     <row r="57">
@@ -2186,25 +2186,25 @@
         <v>28</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>8.59</v>
+        <v>-2.18</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>26.18</v>
+        <v>29.64</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>41.81</v>
+        <v>26.79</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>33.23</v>
+        <v>28.97</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000163955941750188</v>
+        <v>0.000000000000161662381165429</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>20.5132523553922</v>
+        <v>-7.37719234080475</v>
       </c>
     </row>
     <row r="58">
@@ -2212,86 +2212,86 @@
         <v>47</v>
       </c>
       <c r="B58" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C58" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="D58" t="n">
-        <v>6.94</v>
+        <v>-5</v>
       </c>
       <c r="E58" t="n">
-        <v>25.98</v>
+        <v>28.85</v>
       </c>
       <c r="F58" t="n">
-        <v>34.84</v>
+        <v>45.12</v>
       </c>
       <c r="G58" t="n">
-        <v>27.9</v>
+        <v>50.12</v>
       </c>
       <c r="H58" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000161253419152718</v>
+        <v>0.000000000000000000000000000000000000000000000000000072214645848228</v>
       </c>
       <c r="I58" t="n">
-        <v>17.3615698174612</v>
+        <v>-15.3037145862323</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="s">
+      <c r="A59" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B59" t="s">
-        <v>20</v>
-      </c>
-      <c r="C59" t="s">
-        <v>33</v>
-      </c>
-      <c r="D59" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="E59" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0.0000000502596041634182</v>
-      </c>
-      <c r="I59" t="n">
-        <v>-5.45038956618829</v>
+      <c r="B59" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>22.36</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>15.23</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>21.83</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000059749630523613</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>-25.0009146881036</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="s">
+      <c r="A60" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B60" t="s">
-        <v>20</v>
-      </c>
-      <c r="C60" t="s">
-        <v>21</v>
-      </c>
-      <c r="D60" t="n">
-        <v>-2.18</v>
-      </c>
-      <c r="E60" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="F60" t="n">
-        <v>47.94</v>
-      </c>
-      <c r="G60" t="n">
-        <v>50.12</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0.000000671947966015935</v>
-      </c>
-      <c r="I60" t="n">
-        <v>-4.96930069902352</v>
+      <c r="B60" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>-6.68</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>28.03</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>46.53</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>53.21</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000643663064613492</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>-20.4466340005505</v>
       </c>
     </row>
     <row r="61">
@@ -2299,28 +2299,28 @@
         <v>47</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>-4.62</v>
+        <v>-6.93</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>16.4</v>
+        <v>7.12</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>17.22</v>
+        <v>1.98</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>21.83</v>
+        <v>8.9</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>0.0000000000000000000000000000000000000108211354156508</v>
-      </c>
-      <c r="I61" s="2" t="n">
-        <v>-13.0093836414052</v>
+        <v>0</v>
+      </c>
+      <c r="I61" s="2" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="62">
@@ -2328,28 +2328,28 @@
         <v>47</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>-8.11</v>
+        <v>-8.16</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>15.78</v>
+        <v>23.82</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>25.46</v>
+        <v>23.62</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>33.57</v>
+        <v>31.78</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000023614276346955</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000833508175263303</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>-19.9272596818146</v>
+        <v>-27.1908395359493</v>
       </c>
     </row>
     <row r="63">
@@ -2360,25 +2360,25 @@
         <v>24</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>-11.36</v>
+        <v>-8.65</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>13.72</v>
+        <v>6.21</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>21.98</v>
+        <v>2.08</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>33.34</v>
+        <v>10.73</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000242103794285498</v>
-      </c>
-      <c r="I63" s="2" t="n">
-        <v>-28.2312140911904</v>
+        <v>0</v>
+      </c>
+      <c r="I63" s="2" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="64">
@@ -2386,28 +2386,28 @@
         <v>47</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>-11.7</v>
+        <v>-10.45</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>13.38</v>
+        <v>25.73</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>21.09</v>
+        <v>42.51</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>32.8</v>
+        <v>52.96</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000019916163467183</v>
+        <v>9.72367944656562e-225</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>-29.2777481573807</v>
+        <v>-32.0035769510696</v>
       </c>
     </row>
     <row r="65">
@@ -2415,28 +2415,28 @@
         <v>47</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="D65" s="2" t="n">
-        <v>-14.15</v>
+        <v>-10.49</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>12.05</v>
+        <v>22.83</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>19.5</v>
+        <v>25.96</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>33.65</v>
+        <v>36.45</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>2.51519216692383e-274</v>
+        <v>1.64906705105734e-250</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>-35.3890654057141</v>
+        <v>-33.8052889880479</v>
       </c>
     </row>
     <row r="66">
@@ -2444,28 +2444,28 @@
         <v>47</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D66" s="2" t="n">
-        <v>-14.35</v>
+        <v>-11.05</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>11.97</v>
+        <v>9.07</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>19.45</v>
+        <v>4.36</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>33.8</v>
+        <v>15.41</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>1.76344838739284e-281</v>
-      </c>
-      <c r="I66" s="2" t="n">
-        <v>-35.8511700187167</v>
+        <v>0</v>
+      </c>
+      <c r="I66" s="2" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="67">
@@ -2473,57 +2473,57 @@
         <v>47</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D67" s="2" t="n">
-        <v>-14.71</v>
+        <v>-11.94</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>11.74</v>
+        <v>14.14</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>19.05</v>
+        <v>9.43</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>33.76</v>
+        <v>21.37</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>1.07588372062054e-296</v>
-      </c>
-      <c r="I67" s="2" t="n">
-        <v>-36.8146606979389</v>
+        <v>0</v>
+      </c>
+      <c r="I67" s="2" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="s">
+      <c r="A68" t="s">
         <v>47</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D68" s="2" t="n">
-        <v>-14.73</v>
-      </c>
-      <c r="E68" s="2" t="n">
-        <v>11.76</v>
-      </c>
-      <c r="F68" s="2" t="n">
-        <v>19.17</v>
-      </c>
-      <c r="G68" s="2" t="n">
-        <v>33.89</v>
-      </c>
-      <c r="H68" s="2" t="n">
-        <v>1.2728310046915e-296</v>
-      </c>
-      <c r="I68" s="2" t="n">
-        <v>-36.8100976297813</v>
+      <c r="B68" t="s">
+        <v>20</v>
+      </c>
+      <c r="C68" t="s">
+        <v>43</v>
+      </c>
+      <c r="D68" t="n">
+        <v>-12.28</v>
+      </c>
+      <c r="E68" t="n">
+        <v>20.53</v>
+      </c>
+      <c r="F68" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="G68" t="n">
+        <v>34.18</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="69">
@@ -2531,56 +2531,56 @@
         <v>47</v>
       </c>
       <c r="B69" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>-13.48</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>16.84</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="2" t="e">
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>47</v>
+      </c>
+      <c r="B70" t="s">
         <v>16</v>
       </c>
-      <c r="C69" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D69" s="2" t="n">
-        <v>-17.65</v>
-      </c>
-      <c r="E69" s="2" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="F69" s="2" t="n">
-        <v>14.84</v>
-      </c>
-      <c r="G69" s="2" t="n">
-        <v>32.49</v>
-      </c>
-      <c r="H69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" s="2" t="e">
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D70" s="2" t="n">
-        <v>-18.79</v>
-      </c>
-      <c r="E70" s="2" t="n">
-        <v>9.12</v>
-      </c>
-      <c r="F70" s="2" t="n">
-        <v>14.65</v>
-      </c>
-      <c r="G70" s="2" t="n">
-        <v>33.44</v>
-      </c>
-      <c r="H70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" s="2" t="e">
+      <c r="C70" t="s">
+        <v>45</v>
+      </c>
+      <c r="D70" t="n">
+        <v>-13.7</v>
+      </c>
+      <c r="E70" t="n">
+        <v>19.76</v>
+      </c>
+      <c r="F70" t="n">
+        <v>22.03</v>
+      </c>
+      <c r="G70" t="n">
+        <v>35.73</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="e">
         <v>#NUM!</v>
       </c>
     </row>
@@ -2589,22 +2589,22 @@
         <v>47</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>-18.84</v>
+        <v>-15.28</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>8.81</v>
+        <v>9.05</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>13.85</v>
+        <v>6.01</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>32.69</v>
+        <v>21.29</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>0</v>
@@ -2615,25 +2615,25 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D72" s="2" t="n">
-        <v>-19.56</v>
+        <v>52.86</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>12.15</v>
+        <v>74.69</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>27.48</v>
+        <v>68.28</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>47.04</v>
+        <v>15.41</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>0</v>
@@ -2647,22 +2647,22 @@
         <v>48</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>40.58</v>
+        <v>30.48</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>43.7</v>
+        <v>29.05</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>73.93</v>
+        <v>72.66</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>33.34</v>
+        <v>42.18</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>0</v>
@@ -2676,22 +2676,22 @@
         <v>48</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>34.73</v>
+        <v>27.84</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>40.18</v>
+        <v>38.36</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>68.18</v>
+        <v>49.67</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>33.44</v>
+        <v>21.83</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
         <v>48</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>32.95</v>
+        <v>27.08</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>38.93</v>
+        <v>30.22</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>66.75</v>
+        <v>61.26</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>33.8</v>
+        <v>34.18</v>
       </c>
       <c r="H75" s="2" t="n">
         <v>0</v>
@@ -2737,19 +2737,19 @@
         <v>16</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D76" s="2" t="n">
-        <v>20.82</v>
+        <v>25.1</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>31.87</v>
+        <v>28.71</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>54.59</v>
+        <v>60.84</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>33.76</v>
+        <v>35.73</v>
       </c>
       <c r="H76" s="2" t="n">
         <v>0</v>
@@ -2763,28 +2763,28 @@
         <v>48</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="D77" s="2" t="n">
-        <v>18.81</v>
+        <v>9.73</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>30.65</v>
+        <v>22.52</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>52.7</v>
+        <v>38.7</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>33.89</v>
+        <v>28.97</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" s="2" t="e">
-        <v>#NUM!</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000382116988144763</v>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>21.0256509328666</v>
       </c>
     </row>
     <row r="78">
@@ -2792,28 +2792,28 @@
         <v>48</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>17.97</v>
+        <v>9.32</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>32.41</v>
+        <v>19.82</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>45.87</v>
+        <v>62.54</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>27.9</v>
+        <v>53.21</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" s="2" t="e">
-        <v>#NUM!</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000419186311079574</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>18.8311959519209</v>
       </c>
     </row>
     <row r="79">
@@ -2821,28 +2821,28 @@
         <v>48</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>6.37</v>
+        <v>0.65</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>23.47</v>
+        <v>91.67</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>39.79</v>
+        <v>0.79</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>33.42</v>
+        <v>0.15</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>0.000000000000000000000000000000000000000000000000385103614173993</v>
+        <v>0.0000000000000000000000000000000000000000000411063214794192</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>14.7348408321875</v>
+        <v>13.9309136470099</v>
       </c>
     </row>
     <row r="80">
@@ -2850,28 +2850,28 @@
         <v>48</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D80" s="2" t="n">
-        <v>4.88</v>
+        <v>-1.19</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>24.11</v>
+        <v>16.3</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>26.71</v>
+        <v>34.86</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>21.83</v>
+        <v>36.05</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>0.000000000000000000000000000000000000218993138930086</v>
+        <v>0.0127581685921582</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>12.7775010875897</v>
+        <v>-2.49044933086607</v>
       </c>
     </row>
     <row r="81">
@@ -2879,28 +2879,28 @@
         <v>48</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>4.69</v>
+        <v>-2.36</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>21.67</v>
+        <v>15.61</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>51.73</v>
+        <v>29.41</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>47.04</v>
+        <v>31.78</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>0.000000000000000000000000446586059401825</v>
+        <v>0.000000314782513488534</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>10.3437760642853</v>
+        <v>-5.11437436620522</v>
       </c>
     </row>
     <row r="82">
@@ -2908,57 +2908,57 @@
         <v>48</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>4.64</v>
+        <v>-3.76</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>22.42</v>
+        <v>13.9</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>38.39</v>
+        <v>17.61</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>33.75</v>
+        <v>21.37</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>0.00000000000000000000000000639745874121271</v>
+        <v>0.00000000000000000000845624988898511</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>10.7429392643156</v>
+        <v>-9.35378942957887</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="s">
+      <c r="A83" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B83" t="s">
-        <v>26</v>
-      </c>
-      <c r="C83" t="s">
-        <v>32</v>
-      </c>
-      <c r="D83" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E83" t="n">
-        <v>20.53</v>
-      </c>
-      <c r="F83" t="n">
-        <v>34.66</v>
-      </c>
-      <c r="G83" t="n">
-        <v>33.28</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0.00130574660999238</v>
-      </c>
-      <c r="I83" t="n">
-        <v>3.21471374734926</v>
+      <c r="B83" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>-7.36</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>31.89</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>39.26</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>0.000000000000000000000000000000000000000000000000000115856746457886</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>-15.2729254229706</v>
       </c>
     </row>
     <row r="84">
@@ -2966,28 +2966,28 @@
         <v>48</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>1.07</v>
+        <v>-8.13</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>20.34</v>
+        <v>4.08</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>34.64</v>
+        <v>2.6</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>33.57</v>
+        <v>10.73</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>0.0124733230813737</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000114811433206551</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>2.4984628067184</v>
+        <v>-30.223943494948</v>
       </c>
     </row>
     <row r="85">
@@ -2995,28 +2995,28 @@
         <v>48</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>-0.15</v>
+        <v>-8.21</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>0</v>
+        <v>0.69</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>0.15</v>
+        <v>8.9</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>0.000000134941883290294</v>
+        <v>2.65656624922695e-277</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>-5.2720043439448</v>
+        <v>-35.5820352378574</v>
       </c>
     </row>
     <row r="86">
@@ -3024,28 +3024,28 @@
         <v>48</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>-2.45</v>
+        <v>-9.1</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>18.25</v>
+        <v>11.36</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>30.7</v>
+        <v>18.8</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>33.15</v>
+        <v>27.9</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>0.00000000823618320796703</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000567896897043273</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>-5.76355205973258</v>
+        <v>-21.0068406255999</v>
       </c>
     </row>
     <row r="87">
@@ -3053,57 +3053,57 @@
         <v>48</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="D87" s="2" t="n">
-        <v>-4.69</v>
+        <v>-9.86</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>17.97</v>
+        <v>12.99</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>48.27</v>
+        <v>33.11</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>52.96</v>
+        <v>42.98</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>0.000000000000000000000000446586059401824</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000173034015180535</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>-10.3437760642853</v>
+        <v>-20.1718525746832</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="s">
+      <c r="A88" t="s">
         <v>48</v>
       </c>
-      <c r="B88" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D88" s="2" t="n">
-        <v>-5.01</v>
-      </c>
-      <c r="E88" s="2" t="n">
-        <v>16.76</v>
-      </c>
-      <c r="F88" s="2" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="G88" s="2" t="n">
-        <v>33.41</v>
-      </c>
-      <c r="H88" s="2" t="n">
-        <v>0.0000000000000000000000000000000301034652497753</v>
-      </c>
-      <c r="I88" s="2" t="n">
-        <v>-11.8218354329742</v>
+      <c r="B88" t="s">
+        <v>20</v>
+      </c>
+      <c r="C88" t="s">
+        <v>21</v>
+      </c>
+      <c r="D88" t="n">
+        <v>-12.95</v>
+      </c>
+      <c r="E88" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F88" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="G88" t="n">
+        <v>16.84</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="89">
@@ -3111,28 +3111,28 @@
         <v>48</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>-15.29</v>
+        <v>-14.13</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>10.64</v>
+        <v>12</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>17.94</v>
+        <v>34.85</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>33.23</v>
+        <v>48.98</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>1.10384236139509e-304</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000520874745791165</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>-37.3106227401187</v>
+        <v>-28.5283885366699</v>
       </c>
     </row>
     <row r="90">
@@ -3140,28 +3140,28 @@
         <v>48</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>-15.43</v>
+        <v>-15.24</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>10.67</v>
+        <v>4.79</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>18.22</v>
+        <v>6.05</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>33.65</v>
+        <v>21.29</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>1.14973861941767e-307</v>
-      </c>
-      <c r="I90" s="2" t="n">
-        <v>-37.4940903120439</v>
+        <v>0</v>
+      </c>
+      <c r="I90" s="2" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="91">
@@ -3169,22 +3169,22 @@
         <v>48</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>-19.44</v>
+        <v>-19.38</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>8.21</v>
+        <v>10.34</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>13.89</v>
+        <v>30.74</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>33.33</v>
+        <v>50.12</v>
       </c>
       <c r="H91" s="2" t="n">
         <v>0</v>
@@ -3198,22 +3198,22 @@
         <v>48</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>-22.7</v>
+        <v>-26.72</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>10.78</v>
+        <v>4.5</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>27.42</v>
+        <v>9.73</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>50.12</v>
+        <v>36.45</v>
       </c>
       <c r="H92" s="2" t="n">
         <v>0</v>
@@ -3227,22 +3227,22 @@
         <v>48</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>-25.16</v>
+        <v>-44.65</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>4.69</v>
+        <v>6.91</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>7.85</v>
+        <v>31.03</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>33.01</v>
+        <v>75.68</v>
       </c>
       <c r="H93" s="2" t="n">
         <v>0</v>
@@ -3253,25 +3253,25 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>-25.18</v>
+        <v>54.79</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>4.53</v>
+        <v>64.91</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>7.51</v>
+        <v>76.15</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>32.69</v>
+        <v>21.37</v>
       </c>
       <c r="H94" s="2" t="n">
         <v>0</v>
@@ -3282,25 +3282,25 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>-25.47</v>
+        <v>46.27</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>4.26</v>
+        <v>41.79</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>7.02</v>
+        <v>82</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>32.49</v>
+        <v>35.73</v>
       </c>
       <c r="H95" s="2" t="n">
         <v>0</v>
@@ -3311,25 +3311,25 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>-27.95</v>
+        <v>41.66</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>2.91</v>
+        <v>40.41</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>4.85</v>
+        <v>75.83</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>32.8</v>
+        <v>34.18</v>
       </c>
       <c r="H96" s="2" t="n">
         <v>0</v>
@@ -3343,22 +3343,22 @@
         <v>49</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>45.66</v>
+        <v>32.43</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>47.23</v>
+        <v>84.55</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>79.55</v>
+        <v>41.34</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>33.89</v>
+        <v>8.9</v>
       </c>
       <c r="H97" s="2" t="n">
         <v>0</v>
@@ -3368,31 +3368,31 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="s">
+      <c r="A98" t="s">
         <v>49</v>
       </c>
-      <c r="B98" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C98" s="2" t="s">
+      <c r="B98" t="s">
+        <v>18</v>
+      </c>
+      <c r="C98" t="s">
         <v>42</v>
       </c>
-      <c r="D98" s="2" t="n">
-        <v>42.62</v>
-      </c>
-      <c r="E98" s="2" t="n">
-        <v>45.53</v>
-      </c>
-      <c r="F98" s="2" t="n">
-        <v>76.38</v>
-      </c>
-      <c r="G98" s="2" t="n">
-        <v>33.76</v>
-      </c>
-      <c r="H98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" s="2" t="e">
+      <c r="D98" t="n">
+        <v>19.03</v>
+      </c>
+      <c r="E98" t="n">
+        <v>30.63</v>
+      </c>
+      <c r="F98" t="n">
+        <v>46.93</v>
+      </c>
+      <c r="G98" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="e">
         <v>#NUM!</v>
       </c>
     </row>
@@ -3401,28 +3401,28 @@
         <v>49</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>33.37</v>
+        <v>11.06</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>40.08</v>
+        <v>27.44</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>67.02</v>
+        <v>32.9</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>33.65</v>
+        <v>21.83</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I99" s="2" t="e">
-        <v>#NUM!</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000170271409390943</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>27.0798093662706</v>
       </c>
     </row>
     <row r="100">
@@ -3430,28 +3430,28 @@
         <v>49</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>29.03</v>
+        <v>7.25</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>37.41</v>
+        <v>20.69</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>62.83</v>
+        <v>60.46</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>33.8</v>
+        <v>53.21</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" s="2" t="e">
-        <v>#NUM!</v>
+        <v>0.0000000000000000000000000000000000000000000000000000691701289286078</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>15.3065170605382</v>
       </c>
     </row>
     <row r="101">
@@ -3459,57 +3459,57 @@
         <v>49</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>26.01</v>
+        <v>4.91</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>44.1</v>
+        <v>20.12</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>47.84</v>
+        <v>51.95</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>21.83</v>
+        <v>47.04</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" s="2" t="e">
-        <v>#NUM!</v>
+        <v>0.000000000000000000000000546031946190275</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>10.324498851149</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="s">
+      <c r="A102" t="s">
         <v>49</v>
       </c>
-      <c r="B102" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D102" s="2" t="n">
-        <v>22.96</v>
-      </c>
-      <c r="E102" s="2" t="n">
-        <v>29.95</v>
-      </c>
-      <c r="F102" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="G102" s="2" t="n">
-        <v>47.04</v>
-      </c>
-      <c r="H102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I102" s="2" t="e">
-        <v>#NUM!</v>
+      <c r="B102" t="s">
+        <v>28</v>
+      </c>
+      <c r="C102" t="s">
+        <v>30</v>
+      </c>
+      <c r="D102" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="E102" t="n">
+        <v>19.89</v>
+      </c>
+      <c r="F102" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="G102" t="n">
+        <v>28.97</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0.000000000893721215386597</v>
+      </c>
+      <c r="I102" t="n">
+        <v>6.1273190970539</v>
       </c>
     </row>
     <row r="103">
@@ -3520,25 +3520,25 @@
         <v>28</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>20.23</v>
+        <v>1.6</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>32.3</v>
+        <v>18.96</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>53.67</v>
+        <v>40.86</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>33.44</v>
+        <v>39.26</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I103" s="2" t="e">
-        <v>#NUM!</v>
+        <v>0.000573337195478328</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>3.44392383238097</v>
       </c>
     </row>
     <row r="104">
@@ -3546,57 +3546,57 @@
         <v>49</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>13.48</v>
+        <v>-0.15</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>28.2</v>
+        <v>0</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>47.05</v>
+        <v>0</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>33.57</v>
+        <v>0.15</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>4.36209033733548e-215</v>
+        <v>0.000000510804522576793</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>31.3021516010409</v>
+        <v>-5.02220938458581</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="s">
+      <c r="A105" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B105" t="s">
-        <v>20</v>
-      </c>
-      <c r="C105" t="s">
-        <v>38</v>
-      </c>
-      <c r="D105" t="n">
-        <v>5.97</v>
-      </c>
-      <c r="E105" t="n">
-        <v>24.43</v>
-      </c>
-      <c r="F105" t="n">
-        <v>33.87</v>
-      </c>
-      <c r="G105" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="H105" t="n">
-        <v>0.00000000000000000000000000000000000000000000000144158552309114</v>
-      </c>
-      <c r="I105" t="n">
-        <v>14.6453961621452</v>
+      <c r="B105" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>-4.27</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>15.77</v>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>31.78</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>0.000000000000000000000238444621326772</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>-9.723910332857</v>
       </c>
     </row>
     <row r="106">
@@ -3604,28 +3604,28 @@
         <v>49</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>0.58</v>
+        <v>-4.91</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>100</v>
+        <v>16.52</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>0.72</v>
+        <v>48.05</v>
       </c>
       <c r="G106" s="2" t="n">
-        <v>0.15</v>
+        <v>52.96</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000600094310970047</v>
+        <v>0.000000000000000000000000546031946190275</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>15.0133808003726</v>
+        <v>-10.324498851149</v>
       </c>
     </row>
     <row r="107">
@@ -3633,28 +3633,28 @@
         <v>49</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D107" s="2" t="n">
-        <v>-2.56</v>
+        <v>-7.39</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>18.58</v>
+        <v>5.67</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>30.85</v>
+        <v>3.34</v>
       </c>
       <c r="G107" s="2" t="n">
-        <v>33.41</v>
+        <v>10.73</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>0.00000000114299157526037</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000164569436809222</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>-6.08804302750859</v>
+        <v>-28.1633298756628</v>
       </c>
     </row>
     <row r="108">
@@ -3662,57 +3662,57 @@
         <v>49</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D108" s="2" t="n">
-        <v>-5.18</v>
+        <v>-9.38</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>16.97</v>
+        <v>7.13</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>27.83</v>
+        <v>6.03</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>33.01</v>
+        <v>15.41</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>0.000000000000000000000000000000000016008959678034</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000630214917655535</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>-12.4392048623555</v>
+        <v>-29.8610891143855</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="s">
+      <c r="A109" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B109" t="s">
-        <v>28</v>
-      </c>
-      <c r="C109" t="s">
-        <v>29</v>
-      </c>
-      <c r="D109" t="n">
-        <v>-9.53</v>
-      </c>
-      <c r="E109" t="n">
-        <v>14.37</v>
-      </c>
-      <c r="F109" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="G109" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="H109" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000752321262938645</v>
-      </c>
-      <c r="I109" t="n">
-        <v>-23.0790148792663</v>
+      <c r="B109" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>-13.99</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>16.84</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" s="2" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="110">
@@ -3720,28 +3720,28 @@
         <v>49</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>-10.7</v>
+        <v>-18.7</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>13.64</v>
+        <v>2.22</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>22.53</v>
+        <v>2.6</v>
       </c>
       <c r="G110" s="2" t="n">
-        <v>33.23</v>
+        <v>21.29</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000191629585225962</v>
-      </c>
-      <c r="I110" s="2" t="n">
-        <v>-26.0364370331936</v>
+        <v>0</v>
+      </c>
+      <c r="I110" s="2" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="111">
@@ -3749,28 +3749,28 @@
         <v>49</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>-12.9</v>
+        <v>-23.05</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>12.29</v>
+        <v>12.67</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>20.25</v>
+        <v>52.63</v>
       </c>
       <c r="G111" s="2" t="n">
-        <v>33.15</v>
+        <v>75.68</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>1.62051459649029e-219</v>
-      </c>
-      <c r="I111" s="2" t="n">
-        <v>-31.6260216499758</v>
+        <v>0</v>
+      </c>
+      <c r="I111" s="2" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="112">
@@ -3778,28 +3778,28 @@
         <v>49</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D112" s="2" t="n">
-        <v>-15.16</v>
+        <v>-23.5</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>11.09</v>
+        <v>8.06</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>18.59</v>
+        <v>18.68</v>
       </c>
       <c r="G112" s="2" t="n">
-        <v>33.75</v>
+        <v>42.18</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>1.7029667396973e-303</v>
-      </c>
-      <c r="I112" s="2" t="n">
-        <v>-37.2372686957989</v>
+        <v>0</v>
+      </c>
+      <c r="I112" s="2" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="113">
@@ -3807,22 +3807,22 @@
         <v>49</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>-18.87</v>
+        <v>-27.57</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>8.76</v>
+        <v>6.53</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>14.55</v>
+        <v>15.41</v>
       </c>
       <c r="G113" s="2" t="n">
-        <v>33.42</v>
+        <v>42.98</v>
       </c>
       <c r="H113" s="2" t="n">
         <v>0</v>
@@ -3836,22 +3836,22 @@
         <v>49</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>-22.96</v>
+        <v>-27.66</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>11.4</v>
+        <v>7.93</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>30</v>
+        <v>21.32</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>52.96</v>
+        <v>48.98</v>
       </c>
       <c r="H114" s="2" t="n">
         <v>0</v>
@@ -3871,16 +3871,16 @@
         <v>19</v>
       </c>
       <c r="D115" s="2" t="n">
-        <v>-26.47</v>
+        <v>-29.94</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>3.88</v>
+        <v>7.33</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>6.32</v>
+        <v>20.18</v>
       </c>
       <c r="G115" s="2" t="n">
-        <v>32.8</v>
+        <v>50.12</v>
       </c>
       <c r="H115" s="2" t="n">
         <v>0</v>
@@ -3890,118 +3890,31 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="s">
+      <c r="A116" t="s">
         <v>49</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="B116" t="s">
         <v>14</v>
       </c>
-      <c r="C116" s="2" t="s">
+      <c r="C116" t="s">
         <v>15</v>
       </c>
-      <c r="D116" s="2" t="n">
-        <v>-26.79</v>
-      </c>
-      <c r="E116" s="2" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="F116" s="2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="G116" s="2" t="n">
-        <v>32.69</v>
-      </c>
-      <c r="H116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I116" s="2" t="e">
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D117" s="2" t="n">
-        <v>-27.46</v>
-      </c>
-      <c r="E117" s="2" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="F117" s="2" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="G117" s="2" t="n">
-        <v>32.49</v>
-      </c>
-      <c r="H117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I117" s="2" t="e">
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B118" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D118" s="2" t="n">
-        <v>-28.19</v>
-      </c>
-      <c r="E118" s="2" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="F118" s="2" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="G118" s="2" t="n">
-        <v>33.34</v>
-      </c>
-      <c r="H118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I118" s="2" t="e">
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s">
-        <v>49</v>
-      </c>
-      <c r="B119" t="s">
-        <v>20</v>
-      </c>
-      <c r="C119" t="s">
-        <v>21</v>
-      </c>
-      <c r="D119" t="n">
-        <v>-32.55</v>
-      </c>
-      <c r="E119" t="n">
-        <v>7.05</v>
-      </c>
-      <c r="F119" t="n">
-        <v>17.57</v>
-      </c>
-      <c r="G119" t="n">
-        <v>50.12</v>
-      </c>
-      <c r="H119" t="n">
-        <v>0</v>
-      </c>
-      <c r="I119" t="e">
+      <c r="D116" t="n">
+        <v>-31.28</v>
+      </c>
+      <c r="E116" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="F116" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="G116" t="n">
+        <v>36.45</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" t="e">
         <v>#NUM!</v>
       </c>
     </row>

--- a/output/tables/2025/tabla6_v_test.xlsx
+++ b/output/tables/2025/tabla6_v_test.xlsx
@@ -6,26 +6,13 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="AVISO" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="v_test" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="v_test" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
-  <si>
-    <t xml:space="preserve">aviso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">motivo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROVISIONAL - no citar como número final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D2 abierta (PLAN.md): la solución de cluster completa (y por lo tanto qué variables la distinguen) puede cambiar.</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t xml:space="preserve">cluster</t>
   </si>
@@ -515,33 +502,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="7.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="20.71" hidden="0" customWidth="1"/>
@@ -556,42 +516,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>51.14</v>
@@ -614,13 +574,13 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>40.38</v>
@@ -643,13 +603,13 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>38.1</v>
@@ -672,13 +632,13 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>33.12</v>
@@ -701,13 +661,13 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>22.89</v>
@@ -730,13 +690,13 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>12.54</v>
@@ -759,13 +719,13 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>5.93</v>
@@ -788,13 +748,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D9" t="n">
         <v>5.1</v>
@@ -817,13 +777,13 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2.83</v>
@@ -846,13 +806,13 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>-0.1</v>
@@ -875,13 +835,13 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>-3.52</v>
@@ -904,13 +864,13 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>-4.43</v>
@@ -933,13 +893,13 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>-5.93</v>
@@ -962,13 +922,13 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>-7.93</v>
@@ -991,13 +951,13 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>-8.12</v>
@@ -1020,13 +980,13 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>-8.56</v>
@@ -1049,13 +1009,13 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>-9.55</v>
@@ -1078,13 +1038,13 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>-14.33</v>
@@ -1107,13 +1067,13 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>-16.53</v>
@@ -1136,13 +1096,13 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>-20.58</v>
@@ -1165,13 +1125,13 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>-21.47</v>
@@ -1194,13 +1154,13 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>-29.6</v>
@@ -1223,13 +1183,13 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>-30.57</v>
@@ -1252,13 +1212,13 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>-30.83</v>
@@ -1281,13 +1241,13 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>89.27</v>
@@ -1310,13 +1270,13 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>37.18</v>
@@ -1339,13 +1299,13 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>33.62</v>
@@ -1368,13 +1328,13 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>8.44</v>
@@ -1397,13 +1357,13 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>8.39</v>
@@ -1426,13 +1386,13 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>7.97</v>
@@ -1455,13 +1415,13 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>7.34</v>
@@ -1484,13 +1444,13 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>1.87</v>
@@ -1513,13 +1473,13 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>-0.15</v>
@@ -1542,13 +1502,13 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>-1.66</v>
@@ -1571,13 +1531,13 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>-2.32</v>
@@ -1600,13 +1560,13 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D37" s="2" t="n">
         <v>-3.08</v>
@@ -1629,13 +1589,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B38" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C38" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D38" t="n">
         <v>-3.57</v>
@@ -1658,13 +1618,13 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D39" s="2" t="n">
         <v>-3.77</v>
@@ -1687,13 +1647,13 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D40" s="2" t="n">
         <v>-4.65</v>
@@ -1716,13 +1676,13 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D41" s="2" t="n">
         <v>-5.21</v>
@@ -1745,13 +1705,13 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D42" s="2" t="n">
         <v>-5.65</v>
@@ -1774,13 +1734,13 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D43" s="2" t="n">
         <v>-9.19</v>
@@ -1803,13 +1763,13 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D44" s="2" t="n">
         <v>-28.97</v>
@@ -1832,13 +1792,13 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D45" s="2" t="n">
         <v>-36.05</v>
@@ -1861,13 +1821,13 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D46" s="2" t="n">
         <v>-37.18</v>
@@ -1890,13 +1850,13 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D47" s="2" t="n">
         <v>-53.21</v>
@@ -1919,13 +1879,13 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D48" s="2" t="n">
         <v>28.98</v>
@@ -1948,13 +1908,13 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D49" s="2" t="n">
         <v>25.76</v>
@@ -1977,13 +1937,13 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D50" s="2" t="n">
         <v>22.43</v>
@@ -2006,13 +1966,13 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D51" s="2" t="n">
         <v>17.98</v>
@@ -2035,13 +1995,13 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D52" s="2" t="n">
         <v>15.33</v>
@@ -2064,13 +2024,13 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D53" s="2" t="n">
         <v>11.75</v>
@@ -2093,13 +2053,13 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D54" s="2" t="n">
         <v>10.45</v>
@@ -2122,13 +2082,13 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D55" s="2" t="n">
         <v>10.34</v>
@@ -2151,13 +2111,13 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D56" s="2" t="n">
         <v>-0.15</v>
@@ -2180,13 +2140,13 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D57" s="2" t="n">
         <v>-2.18</v>
@@ -2209,13 +2169,13 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B58" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C58" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D58" t="n">
         <v>-5</v>
@@ -2238,13 +2198,13 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D59" s="2" t="n">
         <v>-6.6</v>
@@ -2267,13 +2227,13 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D60" s="2" t="n">
         <v>-6.68</v>
@@ -2296,13 +2256,13 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D61" s="2" t="n">
         <v>-6.93</v>
@@ -2325,13 +2285,13 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D62" s="2" t="n">
         <v>-8.16</v>
@@ -2354,13 +2314,13 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D63" s="2" t="n">
         <v>-8.65</v>
@@ -2383,13 +2343,13 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D64" s="2" t="n">
         <v>-10.45</v>
@@ -2412,13 +2372,13 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D65" s="2" t="n">
         <v>-10.49</v>
@@ -2441,13 +2401,13 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D66" s="2" t="n">
         <v>-11.05</v>
@@ -2470,13 +2430,13 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D67" s="2" t="n">
         <v>-11.94</v>
@@ -2499,13 +2459,13 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B68" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C68" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D68" t="n">
         <v>-12.28</v>
@@ -2528,13 +2488,13 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D69" s="2" t="n">
         <v>-13.48</v>
@@ -2557,13 +2517,13 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B70" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C70" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D70" t="n">
         <v>-13.7</v>
@@ -2586,13 +2546,13 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D71" s="2" t="n">
         <v>-15.28</v>
@@ -2615,13 +2575,13 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D72" s="2" t="n">
         <v>52.86</v>
@@ -2644,13 +2604,13 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D73" s="2" t="n">
         <v>30.48</v>
@@ -2673,13 +2633,13 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D74" s="2" t="n">
         <v>27.84</v>
@@ -2702,13 +2662,13 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D75" s="2" t="n">
         <v>27.08</v>
@@ -2731,13 +2691,13 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D76" s="2" t="n">
         <v>25.1</v>
@@ -2760,13 +2720,13 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D77" s="2" t="n">
         <v>9.73</v>
@@ -2789,13 +2749,13 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D78" s="2" t="n">
         <v>9.32</v>
@@ -2818,13 +2778,13 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D79" s="2" t="n">
         <v>0.65</v>
@@ -2847,13 +2807,13 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D80" s="2" t="n">
         <v>-1.19</v>
@@ -2876,13 +2836,13 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D81" s="2" t="n">
         <v>-2.36</v>
@@ -2905,13 +2865,13 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D82" s="2" t="n">
         <v>-3.76</v>
@@ -2934,13 +2894,13 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D83" s="2" t="n">
         <v>-7.36</v>
@@ -2963,13 +2923,13 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D84" s="2" t="n">
         <v>-8.13</v>
@@ -2992,13 +2952,13 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D85" s="2" t="n">
         <v>-8.21</v>
@@ -3021,13 +2981,13 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D86" s="2" t="n">
         <v>-9.1</v>
@@ -3050,13 +3010,13 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D87" s="2" t="n">
         <v>-9.86</v>
@@ -3079,13 +3039,13 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B88" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C88" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D88" t="n">
         <v>-12.95</v>
@@ -3108,13 +3068,13 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D89" s="2" t="n">
         <v>-14.13</v>
@@ -3137,13 +3097,13 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D90" s="2" t="n">
         <v>-15.24</v>
@@ -3166,13 +3126,13 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D91" s="2" t="n">
         <v>-19.38</v>
@@ -3195,13 +3155,13 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D92" s="2" t="n">
         <v>-26.72</v>
@@ -3224,13 +3184,13 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D93" s="2" t="n">
         <v>-44.65</v>
@@ -3253,13 +3213,13 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D94" s="2" t="n">
         <v>54.79</v>
@@ -3282,13 +3242,13 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D95" s="2" t="n">
         <v>46.27</v>
@@ -3311,13 +3271,13 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D96" s="2" t="n">
         <v>41.66</v>
@@ -3340,13 +3300,13 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D97" s="2" t="n">
         <v>32.43</v>
@@ -3369,13 +3329,13 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B98" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C98" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D98" t="n">
         <v>19.03</v>
@@ -3398,13 +3358,13 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D99" s="2" t="n">
         <v>11.06</v>
@@ -3427,13 +3387,13 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D100" s="2" t="n">
         <v>7.25</v>
@@ -3456,13 +3416,13 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D101" s="2" t="n">
         <v>4.91</v>
@@ -3485,13 +3445,13 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B102" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C102" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D102" t="n">
         <v>2.66</v>
@@ -3514,13 +3474,13 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D103" s="2" t="n">
         <v>1.6</v>
@@ -3543,13 +3503,13 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D104" s="2" t="n">
         <v>-0.15</v>
@@ -3572,13 +3532,13 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D105" s="2" t="n">
         <v>-4.27</v>
@@ -3601,13 +3561,13 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D106" s="2" t="n">
         <v>-4.91</v>
@@ -3630,13 +3590,13 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D107" s="2" t="n">
         <v>-7.39</v>
@@ -3659,13 +3619,13 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D108" s="2" t="n">
         <v>-9.38</v>
@@ -3688,13 +3648,13 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D109" s="2" t="n">
         <v>-13.99</v>
@@ -3717,13 +3677,13 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D110" s="2" t="n">
         <v>-18.7</v>
@@ -3746,13 +3706,13 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D111" s="2" t="n">
         <v>-23.05</v>
@@ -3775,13 +3735,13 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D112" s="2" t="n">
         <v>-23.5</v>
@@ -3804,13 +3764,13 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D113" s="2" t="n">
         <v>-27.57</v>
@@ -3833,13 +3793,13 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D114" s="2" t="n">
         <v>-27.66</v>
@@ -3862,13 +3822,13 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D115" s="2" t="n">
         <v>-29.94</v>
@@ -3891,13 +3851,13 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B116" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C116" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D116" t="n">
         <v>-31.28</v>

--- a/output/tables/2025/tabla6_v_test.xlsx
+++ b/output/tables/2025/tabla6_v_test.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Sin inseguridad en la casa</t>
   </si>
   <si>
-    <t xml:space="preserve">comgen_per_pct_cat</t>
+    <t xml:space="preserve">comgen_per_cat</t>
   </si>
   <si>
     <t xml:space="preserve">Una o dos medidas en la vivienda</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">No gasta en medidas de seguridad</t>
   </si>
   <si>
-    <t xml:space="preserve">comgen_com_pct_cat</t>
+    <t xml:space="preserve">comgen_com_cat</t>
   </si>
   <si>
     <t xml:space="preserve">Sin medidas en el barrio</t>
